--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -511,7 +511,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -536,7 +536,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -561,7 +561,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -586,7 +586,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -611,7 +611,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -636,7 +636,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -661,7 +661,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -686,7 +686,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -711,7 +711,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -736,7 +736,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -761,7 +761,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -786,7 +786,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -811,7 +811,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -836,7 +836,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -861,7 +861,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -886,7 +886,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -911,7 +911,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -936,7 +936,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -961,7 +961,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -986,7 +986,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1011,7 +1011,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1036,7 +1036,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1061,7 +1061,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1086,7 +1086,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1111,7 +1111,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1136,7 +1136,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1161,7 +1161,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1186,7 +1186,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1211,7 +1211,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1236,7 +1236,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1261,7 +1261,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1286,7 +1286,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1311,7 +1311,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1336,7 +1336,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1361,7 +1361,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1386,7 +1386,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1411,7 +1411,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1436,7 +1436,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1461,7 +1461,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1486,7 +1486,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1511,7 +1511,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1536,7 +1536,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1561,7 +1561,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1586,7 +1586,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1611,7 +1611,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1636,7 +1636,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1661,7 +1661,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1686,7 +1686,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1711,7 +1711,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1736,7 +1736,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1761,7 +1761,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1786,7 +1786,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1811,7 +1811,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1836,7 +1836,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1861,7 +1861,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1886,7 +1886,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1911,7 +1911,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1936,7 +1936,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1961,7 +1961,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1986,7 +1986,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2011,7 +2011,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2036,7 +2036,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2061,7 +2061,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2086,7 +2086,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2111,7 +2111,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2136,7 +2136,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2147,31 +2147,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3099,7 +3074,7 @@
     <row r="19" ht="78" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3109,7 +3084,7 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -3118,21 +3093,21 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0BH325183_1.png, 0BH325183_2.png</t>
+          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-tmp-6/item-pic-2a3c594b7813848476bc066f768e0f1d.jpg</t>
         </is>
       </c>
     </row>
     <row r="20" ht="78" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3146,26 +3121,26 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0BH325183 B_1.png, 0BH325183 B_2.png</t>
+          <t>0BH325183_1.png, 0BH325183_2.png</t>
         </is>
       </c>
     </row>
     <row r="21" ht="78" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3175,23 +3150,23 @@
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0BH325183B_1.png, 0BH325183B_2.png, 0BH325183B_3.png</t>
+          <t>0BH325183 B_1.png, 0BH325183 B_2.png</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3286,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM 0CW</t>
+          <t>Мехатроник DSG7 подходит на ВСЕ DQ200 0am 0cw</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -4561,7 +4536,7 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -4577,14 +4552,14 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>DQ500_1.png, DQ500_3.png, DQ500_a-2.png, dq500.png</t>
+          <t>DQ500-a-1.png, DQ500_1.png, DQ500_3.png, DQ500_a-2.png, dq500.png</t>
         </is>
       </c>
     </row>
     <row r="64" ht="78" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>DQ500-a</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4594,30 +4569,30 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DSG7 DQ500 0BH</t>
+          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла</t>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>DQ500-a-1.png</t>
+          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
         </is>
       </c>
     </row>
     <row r="65" ht="78" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4631,26 +4606,26 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
+          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
+          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
         </is>
       </c>
     </row>
     <row r="66" ht="78" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4664,26 +4639,26 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
+          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-9/14860646217.jpg</t>
         </is>
       </c>
     </row>
     <row r="67" ht="78" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4693,30 +4668,30 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра EA888</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png</t>
+          <t>EA888_1.png</t>
         </is>
       </c>
     </row>
     <row r="68" ht="78" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4726,30 +4701,30 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра EA888</t>
+          <t>EA888 Gen.3 магнит + корпус алюминиевый комплект</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>EA888_1.png</t>
+          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
         </is>
       </c>
     </row>
     <row r="69" ht="78" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4759,30 +4734,30 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>EA888 Gen.3 магнит + корпус алюминиевый комплект</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
+          <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
         </is>
       </c>
     </row>
     <row r="70" ht="78" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4792,30 +4767,30 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
+          <t>TEST001_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="71" ht="78" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4829,31 +4804,31 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>TEST001_2.jpg</t>
+          <t>WHT001922_1.png</t>
         </is>
       </c>
     </row>
     <row r="72" ht="78" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Действующий</t>
+          <t>Новый (черновик)</t>
         </is>
       </c>
       <c r="C72" s="2" t="n"/>
@@ -4862,26 +4837,26 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
-        </is>
-      </c>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
+        </is>
+      </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>WHT001922_1.png</t>
+          <t>filtr-setka-0b5-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="73" ht="78" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4891,96 +4866,96 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
+          <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig_1.png</t>
+          <t>gidroakkumulyator-orig_1.png, gidroakkumulyator-orig_2.png</t>
         </is>
       </c>
     </row>
     <row r="74" ht="78" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
+          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
-        </is>
-      </c>
+      <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig_1.png, gidroakkumulyator-orig_2.png</t>
+          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
         </is>
       </c>
     </row>
     <row r="75" ht="78" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Действующий</t>
+          <t>Новый (черновик)</t>
         </is>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
-        </is>
-      </c>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт (на 2 штока)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
+        </is>
+      </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
+          <t>klipsy-shtokov-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="76" ht="78" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4990,35 +4965,35 @@
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт (на 2 штока)</t>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
+          <t>Найден через next.png/next-2.png ещё раньше. Отдельный корпус фильтра 0BH325159 — сейчас в каталоге есть только 0BH325183B (сам фильтр) и наборы DQ500/DQ500-a/Dq500 (корпус+фильтр вместе). Образец — 0BH325183B.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht_1.png</t>
+          <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
         </is>
       </c>
     </row>
     <row r="77" ht="78" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C77" s="2" t="n"/>
@@ -5027,19 +5002,15 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Накладка на автомобиль на педали, 3 шт.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Найден через next.png/next-2.png ещё раньше. Отдельный корпус фильтра 0BH325159 — сейчас в каталоге есть только 0BH325183B (сам фильтр) и наборы DQ500/DQ500-a/Dq500 (корпус+фильтр вместе). Образец — 0BH325183B.</t>
-        </is>
-      </c>
+      <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
+          <t>nakladki-pedali_1.png, nakladki-pedali_2.png</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5776,58 +5747,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TESTWB001_2.jpg</t>
+          <t>0BH325183B_1.png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>0BH325183B</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nakladki-pedali_1.png</t>
+          <t>0BH325183B_2.png</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>0BH325183B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nakladki-pedali_2.png</t>
+          <t>0BH325183B_3.png</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>0BH325183B</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>next-2.png</t>
+          <t>TESTWB001_2.jpg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>TESTWB001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>next-2.png</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>next.png</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>next</t>
         </is>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нераспознанные фото" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Товары" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Нераспознанные фото" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>2</col>
@@ -171,13 +171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -196,13 +196,38 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -217,17 +242,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -242,17 +267,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -267,17 +317,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -292,17 +342,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -317,17 +367,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -342,17 +392,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -367,17 +417,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -392,17 +442,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -417,17 +467,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -442,17 +517,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -467,17 +542,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -492,17 +567,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -517,17 +617,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -542,17 +642,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -567,17 +667,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -592,17 +692,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -617,17 +717,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -642,17 +742,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -667,17 +767,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -692,17 +792,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -717,17 +817,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -742,17 +842,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -767,17 +867,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -792,17 +892,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -817,17 +917,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -842,17 +942,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -867,17 +992,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -892,17 +1042,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -917,17 +1092,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -942,17 +1117,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -967,17 +1142,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -992,17 +1192,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1017,17 +1217,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1042,17 +1242,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1067,17 +1267,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1092,17 +1292,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1117,17 +1317,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1142,17 +1342,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1167,17 +1392,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1192,17 +1442,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1217,17 +1467,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1242,17 +1517,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1267,17 +1542,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1292,17 +1592,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1317,17 +1617,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1342,17 +1642,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1367,17 +1667,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1392,17 +1692,92 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1417,17 +1792,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1442,17 +1842,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1467,17 +1867,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1492,17 +1892,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1517,17 +1917,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1542,17 +1942,42 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1567,17 +1992,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1592,17 +2017,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1617,17 +2042,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1642,17 +2067,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1667,17 +2092,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1692,17 +2117,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1717,17 +2142,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1742,17 +2167,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1767,17 +2192,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1792,17 +2217,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1817,17 +2242,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1842,17 +2267,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1867,17 +2292,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1892,17 +2317,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1917,17 +2342,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1942,17 +2367,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1967,17 +2392,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1992,17 +2417,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2017,17 +2442,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2042,17 +2467,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2067,17 +2492,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2092,17 +2517,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2117,17 +2542,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2142,17 +2567,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2589,7 +3014,7 @@
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -2605,7 +3030,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-y/7394698654.jpg</t>
+          <t>02E305051C_1.jpg</t>
         </is>
       </c>
     </row>
@@ -2688,7 +3113,7 @@
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -2704,7 +3129,7 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-s/7397498764.jpg</t>
+          <t>0AM301212A_1.jpg</t>
         </is>
       </c>
     </row>
@@ -2898,7 +3323,11 @@
           <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #dsg_ремонт #dsg_обслуживание #dq2000amdsg</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -2952,7 +3381,7 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -2968,7 +3397,7 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-n/7770051311.jpg</t>
+          <t>0AM325473_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3459,11 @@
           <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg7 #dsg7_dq200 #dsg7_mechatronic #электроннаяплатаdq200</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -3084,7 +3517,7 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -3100,7 +3533,7 @@
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-tmp-6/item-pic-2a3c594b7813848476bc066f768e0f1d.jpg</t>
+          <t>0BH325_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3715,7 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -3294,11 +3727,15 @@
           <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #мехатроник_dq200 #dsg7 #dsg7_dq200 #dsg7_0am_dq200 #0am325066ae #0am325066ac #0am325066 #dq200ремкомплект #0am325025 #0am325025d</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0am325025H-1.png</t>
+          <t>0am325025H-1.png, 0am325025H_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3764,11 @@
           <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -3393,7 +3834,11 @@
           <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -3492,7 +3937,11 @@
           <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -3579,7 +4028,7 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -3595,7 +4044,7 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-g/7768630888.jpg</t>
+          <t>0am325025n_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3645,7 +4094,7 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -3661,7 +4110,7 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-w/9080035556.jpg</t>
+          <t>0am325025r_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3711,7 +4160,7 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -3723,11 +4172,15 @@
           <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-p/8577082285.jpg</t>
+          <t>0am325025x_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3843,7 +4296,7 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -3859,7 +4312,7 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-q/7563423914.jpg</t>
+          <t>0am325066ad_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3921,7 +4374,11 @@
           <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -4107,7 +4564,7 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -4119,11 +4576,15 @@
           <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdsg7dq200</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-f/8529361611.jpg</t>
+          <t>0cw0am_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4613,11 @@
           <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкиdq200</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -4173,7 +4638,7 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -4185,11 +4650,15 @@
           <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200dsg</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-m/8529439774.jpg</t>
+          <t>0cw0amdsgdq200_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4687,11 @@
           <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4745,7 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -4288,7 +4761,7 @@
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-q/7418270474.jpg</t>
+          <t>122390AK-AF_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4844,7 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -4383,11 +4856,15 @@
           <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf011e</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-f/10611206151.jpg</t>
+          <t>31705-1XF0C_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4893,11 @@
           <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -4569,7 +5050,7 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -4581,11 +5062,15 @@
           <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
+          <t>Dq200dsg7_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4602,7 +5087,7 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -4618,7 +5103,7 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
+          <t>Dq200dsg70am0cw_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4635,7 +5120,7 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -4651,7 +5136,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-9/14860646217.jpg</t>
+          <t>Dq500_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4680,7 +5165,11 @@
           <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>#корпусмасляногофильтраEA888</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4701,7 +5190,7 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -4717,7 +5206,7 @@
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
+          <t>EA888gen3_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4899,7 +5388,7 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -4915,7 +5404,7 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
+          <t>jf011e_1.jpg</t>
         </is>
       </c>
     </row>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -211,17 +211,42 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -242,11 +267,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -267,11 +317,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -292,11 +342,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -317,11 +367,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -342,11 +392,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -367,11 +417,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -392,11 +442,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -417,11 +467,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -442,11 +517,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -467,11 +542,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -492,11 +567,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -517,11 +617,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -542,11 +642,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -567,11 +667,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -592,11 +692,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -617,11 +717,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -642,11 +742,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -667,11 +767,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -692,11 +792,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -717,11 +817,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -742,11 +842,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -767,11 +867,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -792,11 +892,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -817,11 +917,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -842,11 +942,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -867,11 +992,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -892,11 +1042,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -917,11 +1092,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -942,11 +1117,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -967,11 +1142,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -992,11 +1192,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1017,11 +1217,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1042,11 +1242,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1067,11 +1267,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1092,11 +1292,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1117,11 +1317,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1142,11 +1342,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1167,11 +1392,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1192,11 +1442,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1217,11 +1467,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1242,11 +1517,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1267,11 +1542,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1292,11 +1592,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1317,11 +1617,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1342,11 +1642,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1367,11 +1667,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1392,11 +1692,86 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1417,11 +1792,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1442,11 +1842,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1467,11 +1867,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1492,11 +1892,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1517,11 +1917,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1542,11 +1942,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1567,11 +1992,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1592,11 +2017,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1617,11 +2042,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1642,11 +2067,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1667,11 +2092,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1692,11 +2117,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1717,11 +2142,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1742,11 +2167,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1767,11 +2192,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1792,11 +2217,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1817,11 +2242,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1842,11 +2267,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1867,11 +2292,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1892,11 +2317,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1917,11 +2342,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1942,11 +2367,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1967,11 +2392,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1992,11 +2417,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2017,11 +2442,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2042,11 +2467,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2067,11 +2492,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2092,11 +2517,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2117,11 +2542,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2142,11 +2567,61 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2449,7 +2924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2527,12 +3002,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий</t>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X301127C</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -2560,12 +3035,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод</t>
+          <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -2589,23 +3064,23 @@
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DQ250 02E DSG6</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество</t>
+          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-y/7394698654.jpg</t>
+          <t>02E305051C_1.jpg, 02E305051C_1.png</t>
         </is>
       </c>
     </row>
@@ -2626,10 +3101,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DQ250 DSG6 с платой 02E927770AL</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -2659,12 +3138,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева</t>
+          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -2688,23 +3167,23 @@
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП DSG7 DQ200 0AM 0CW</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-s/7397498764.jpg</t>
+          <t>0AM301212A_1.jpg, 0AM301212A_1.png</t>
         </is>
       </c>
     </row>
@@ -2725,12 +3204,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG 7 DQ200 0AM 0CW регулятор давления 1 шт</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325025B.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -2758,12 +3237,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM 0CW 1 шт</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -2791,12 +3270,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!</t>
+          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -2820,23 +3299,23 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A_1.png, 0AM325413A_2.png, 0AM325413A_3.png, 0AM325413A_4.png, 0AM325413A_5.png, 0AM325413A_6.png, 0AM325413A_7.png</t>
+          <t>0AM325413A_1.png</t>
         </is>
       </c>
     </row>
@@ -2857,12 +3336,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр</t>
+          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -2890,12 +3369,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника с утолщением DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.</t>
+          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -2923,12 +3402,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG сепараторная пластина под плиту мехатроника DSG7 DQ200 0am 0cw</t>
+          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -2952,23 +3431,23 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-n/7770051311.jpg</t>
+          <t>0AM325473_1.jpg, 0AM325473_1.png</t>
         </is>
       </c>
     </row>
@@ -2985,23 +3464,23 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0AM325587E-apng.png, 0AM325587E_1.png, 0AM325587E_2.png, 0AM325587E_3.png, 0AM325587E_4.png</t>
+          <t>0AM325587E_1.png, 0AM325587E_2.png, 0AM325587E_3.png, 0AM325587E_4.png</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3506,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -3055,12 +3534,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Прокладки платы DSG7 DQ200 0AM 0CW</t>
+          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -3084,23 +3563,23 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-tmp-6/item-pic-2a3c594b7813848476bc066f768e0f1d.jpg</t>
+          <t>0BH325_1.jpg, 0BH325_1.png, 0BH325_2.png, 0BH325_3.png</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3600,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -3154,12 +3633,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -3187,12 +3666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 с прокладками и гидроплитой Плита, сальники, уплотнения</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -3220,12 +3699,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -3253,12 +3732,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200 0AM 0CW 2 пыльника 2 сальника 2 крышки</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов</t>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -3282,23 +3761,23 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 подходит на ВСЕ DQ200 0am 0cw</t>
+          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.</t>
+          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0am325025H-1.png</t>
+          <t>0am325025H-1.png, 0am325025H_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3319,12 +3798,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 c эл. платой 0AM927769D в сборе</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!</t>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -3352,12 +3831,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
+          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025P.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -3385,12 +3864,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG крышка мехатроника DSG7 + Усиленная с утолщением прокладка крышки dq200</t>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках</t>
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -3418,12 +3897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Болты мехатроника DSG7DQ200 (0AM/0CW) комплект 7 шт. (4 M890 WHT001922 + 3 M835 WHT001922/01X301127C</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии</t>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -3451,12 +3930,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200 (0AM 0CW) сальник, пыльник, крышка</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -3484,12 +3963,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 dq200 оригинал VAG сепараторная пластина мехатроника + пластины на соленоиды</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)</t>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -3517,12 +3996,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -3550,12 +4029,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -3579,23 +4058,23 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-g/7768630888.jpg</t>
+          <t>0am325025n_1.jpg, 0am325025n_1.png</t>
         </is>
       </c>
     </row>
@@ -3616,12 +4095,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -3645,23 +4124,23 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-w/9080035556.jpg</t>
+          <t>0am325025r_1.png</t>
         </is>
       </c>
     </row>
@@ -3682,12 +4161,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект: длинный шток 101мм 0AM325091E + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025u.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -3711,23 +4190,23 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM Новые соленоиды Bosch</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.</t>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-p/8577082285.jpg</t>
+          <t>0am325025x_1.jpg</t>
         </is>
       </c>
     </row>
@@ -3748,12 +4227,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091F 99 мм + втулка (гильза) мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект: короткий шток 99мм 0AM325091F + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат</t>
+          <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025z.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -3781,12 +4260,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025С.&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -3814,12 +4293,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -3843,23 +4322,23 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Сальник манжет штока сцепления мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-q/7563423914.jpg</t>
+          <t>0am325066ad_1.jpg, 0am325066ad_1.png</t>
         </is>
       </c>
     </row>
@@ -3876,23 +4355,23 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae_1.png, 0am325066ae_2.png, 0am325066ae_3.png, 0am325066ae_4.png, 0am325066ae_5.png, 0am325066ae_6.png</t>
+          <t>0am325066ae_1.png, 0am325066ae_4.png</t>
         </is>
       </c>
     </row>
@@ -3913,12 +4392,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0AM325091E</t>
+          <t>Шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!</t>
+          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -3946,10 +4425,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Комплект: 2 штока 0AM325091E (101мм) усиленные + 2 втулки (гильзы) мехатроника DSG7 DQ200 0AM/0CW</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -3979,12 +4462,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 0AM 0CW 0am325091f (99 мм) короткий 1шт</t>
+          <t>Шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!</t>
+          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -4012,10 +4495,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Комплект: 2 штока 0AM325091F (99мм) короткие усиленные + 2 втулки (гильзы) мехатроника DSG7 DQ200 0AM/0CW</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -4041,23 +4528,23 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM325477AE</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae_1.png, 0am325477ae_2.png, 0am325477ae_3.png, 0am325477ae_4.png, 0am325477ae_5.png</t>
+          <t>0am325477ae_1.png, 0am325477ae_2.png, 0am325477ae_3.png, 0am325477ae_4.png</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4565,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников DSG7 DQ200 0AM 0CW, 10 шт оригинал NSK, для VW / Audi / Skoda</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!</t>
+          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -4107,23 +4594,23 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы 0am 0cw dq200 dsg 7</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-f/8529361611.jpg</t>
+          <t>0cw0am_1.jpg, 0cw0am_1.png</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4631,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыльники и сальники W</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;</t>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -4173,23 +4660,23 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение резиновое электромотора гидроблока (мехатроника) DQ200 0AM DSG 7</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !</t>
+          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-m/8529439774.jpg</t>
+          <t>0cw0amdsgdq200_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4697,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы электронной мехатроника DSG7 DQ200 0am 0cw</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.</t>
+          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -4243,12 +4730,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Сальник штока мехатроника DSG7 DQ200 0AM / 0CW оригинал Volkswagen</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -4272,23 +4759,23 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-q/7418270474.jpg</t>
+          <t>122390AK-AF_1.jpg, 122390AK-AF_1.png</t>
         </is>
       </c>
     </row>
@@ -4309,12 +4796,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал Volkswagen Германия</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -4342,12 +4829,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG 7 0B5 DL501 (123014 AF), аналог 0B5 325 421 для N436 / N440, Audi Q5 A4 A5</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -4371,23 +4858,23 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E Старое поколение (RE0F10A) 2 датчика</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e</t>
+          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-f/10611206151.jpg</t>
+          <t>31705-1XF0C_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4408,12 +4895,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, Renault, Mitsubishi Новый</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор</t>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -4441,12 +4928,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT для Nissan, Renault, Mitsubishi</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan</t>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -4474,12 +4961,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 / 5636119 для Chevrolet, Opel (Astra J, Insignia, Cruze, Aveo)</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -4507,10 +4994,14 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30 6T40 6T45 6T50 Chevrolet Cruze, Opel</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -4540,12 +5031,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DSG7 DQ500 0BH</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла</t>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -4569,23 +5060,23 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
+          <t>Dq200dsg7_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4602,23 +5093,23 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
+          <t>Dq200dsg70am0cw_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4635,23 +5126,23 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-9/14860646217.jpg</t>
+          <t>Dq500_1.jpg, Dq500_2.png</t>
         </is>
       </c>
     </row>
@@ -4672,12 +5163,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра EA888</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -4701,23 +5192,23 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>EA888 Gen.3 магнит + корпус алюминиевый комплект</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!</t>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
+          <t>EA888gen3_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4738,12 +5229,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
@@ -4804,12 +5295,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -4840,7 +5331,11 @@
           <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4866,14 +5361,18 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4882,7 +5381,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig_1.png, gidroakkumulyator-orig_2.png</t>
+          <t>gidroakkumulyator-orig_1.png, gidroakkumulyator-orig_2.png, gidroakkumulyator-orig_3.png</t>
         </is>
       </c>
     </row>
@@ -4899,11 +5398,11 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4915,7 +5414,7 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
+          <t>jf011e_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4936,10 +5435,14 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт (на 2 штока)</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4969,10 +5472,14 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159 (без фильтра)</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+        </is>
+      </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -5002,10 +5509,14 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Накладка на автомобиль на педали, 3 шт.</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
@@ -5031,10 +5542,14 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Планки соленоидов DSG7 DQ200, комплект 2 шт на весь мехатроник</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr"/>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -5064,10 +5579,14 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды Volkswagen мехатроника DQ200 DSG7 (без сепараторной пластины)</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr"/>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -5097,10 +5616,14 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита мехатроника + фильтр DSG7 DQ200 0AM/0CW, комплект</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -5130,10 +5653,14 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита мехатроника + фильтр + 2 пыльника штоков DSG7 DQ200 0AM/0CW, комплект</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5690,14 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 пыльника ОРИГИНАЛ Volkswagen DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -5196,10 +5727,14 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита мехатроника + фильтр + 2 пыльника + 2 сальника DSG7 DQ200 0AM/0CW, полный комплект</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5229,10 +5764,14 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 сальника ОРИГИНАЛ Volkswagen DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr"/>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -5262,10 +5801,14 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Подшипники вилки 6-й передачи и заднего хода DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
+        </is>
+      </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -5295,10 +5838,14 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный комплект пыльников штоков VAG, 2 шт DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr"/>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5875,14 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект штоков VAG (2 пыльника + 2 сальника + 2 крышки) DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -5361,10 +5912,14 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -5394,10 +5949,14 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый сальник толкателя с гальваническим покрытием DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr"/>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+        </is>
+      </c>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -5430,7 +5989,11 @@
           <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+        </is>
+      </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -5460,10 +6023,14 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный комплект сальников штоков VAG, 2 шт DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+        </is>
+      </c>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -5493,10 +6060,14 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода (левый) DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
+          <t>Сальник привода левый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+        </is>
+      </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5526,10 +6097,14 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода (правый) DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr"/>
+          <t>Сальник привода правый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+        </is>
+      </c>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -5562,7 +6137,11 @@
           <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5595,7 +6174,11 @@
           <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+        </is>
+      </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -5625,10 +6208,14 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка плиты мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+        </is>
+      </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5658,10 +6245,14 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Комплект толкателей вилок (поршней) 4 шт + сальники 4 шт DSG7 DQ200, на весь мехатроник</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr"/>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+        </is>
+      </c>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -5694,7 +6285,11 @@
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+        </is>
+      </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5704,6 +6299,80 @@
       <c r="I98" s="2" t="inlineStr">
         <is>
           <t>vtulki-shtokov-2sht_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="78" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Новый (черновик)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht_1.png, salniki-tolkatelya-4sht_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="78" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Новый (черновик)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt_1.png</t>
         </is>
       </c>
     </row>
@@ -5721,24 +6390,19 @@
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Файл</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Похожий артикул</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -3024,7 +3024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N113"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3036,11 +3036,12 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3091,25 +3092,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Остаток, шт.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Цена WB, ₽ (только для новых WB-товаров)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Описание</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Хэштеги / Теги</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Заметки</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Файлы (папка photos/)</t>
         </is>
@@ -3152,14 +3158,15 @@
         <v>1500</v>
       </c>
       <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>01X301127C_1.png</t>
         </is>
@@ -3198,14 +3205,15 @@
         <v>10000</v>
       </c>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>02E 305 045_1.png, 02E 305 045_2.png, 02E 305 045_3.png</t>
         </is>
@@ -3248,14 +3256,15 @@
         <v>3000</v>
       </c>
       <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>02E305051C_1.jpg, 02E305051C_1.png</t>
         </is>
@@ -3294,18 +3303,19 @@
         <v>145000</v>
       </c>
       <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Подтверждено пользователем: это целый мехатроник в сборе с электронной платой (DQ250/DSG6), не отдельная плата. Образец поменяла на 0am325025HX — тоже 'мехатроник с эл. платой в сборе', ближе по смыслу, чем фильтр 02E305051C.</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>02E927770AL_1.png</t>
         </is>
@@ -3348,14 +3358,15 @@
         <v>5000</v>
       </c>
       <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>02e305045_1.png, 02e305045_2.png, 02e305045_3.png, 02e305045_4.png</t>
         </is>
@@ -3398,14 +3409,15 @@
         <v>2500</v>
       </c>
       <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0AM301212A_1.jpg, 0AM301212A_1.png</t>
         </is>
@@ -3448,14 +3460,15 @@
         <v>12000</v>
       </c>
       <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325025B.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0AM325025B_1.png, 0AM325025B_2.png, 0AM325025B_3.png</t>
         </is>
@@ -3486,7 +3499,8 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -3506,9 +3520,9 @@
 Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -3551,14 +3565,15 @@
         <v>1500</v>
       </c>
       <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0AM325120A_1.png</t>
         </is>
@@ -3601,14 +3616,15 @@
         <v>4500</v>
       </c>
       <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0AM325219C_1.png, 0AM325219C_2.png</t>
         </is>
@@ -3651,14 +3667,15 @@
         <v>1500</v>
       </c>
       <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0AM325413A_1.png</t>
         </is>
@@ -3701,14 +3718,15 @@
         <v>2000</v>
       </c>
       <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0AM325433E_1.png, 0AM325433E_2.png</t>
         </is>
@@ -3751,18 +3769,19 @@
         <v>3000</v>
       </c>
       <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #dsg_ремонт #dsg_обслуживание #dq2000amdsg</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0AM325443D_1.png, 0AM325443D_2.png, 0AM325443D_3.png</t>
         </is>
@@ -3805,14 +3824,15 @@
         <v>3500</v>
       </c>
       <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0AM325467J_1.png, 0AM325467J_2.png</t>
         </is>
@@ -3855,14 +3875,15 @@
         <v>15000</v>
       </c>
       <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0AM325473_1.jpg, 0AM325473_1.png</t>
         </is>
@@ -3905,14 +3926,15 @@
         <v>12000</v>
       </c>
       <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0AM325587E_1.png, 0AM325587E_2.png, 0AM325587E_3.png, 0AM325587E_4.png</t>
         </is>
@@ -3955,18 +3977,19 @@
         <v>80000</v>
       </c>
       <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>#dq200 #dq200ремкомплект #dq200_0am #dsg7 #dsg7_dq200 #dsg7_mechatronic #электроннаяплатаdq200</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0AM927769D_1.png</t>
         </is>
@@ -4005,14 +4028,15 @@
         <v>4500</v>
       </c>
       <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0AM927769N_1.png, 0AM927769N_2.png</t>
         </is>
@@ -4051,14 +4075,15 @@
         <v>6000</v>
       </c>
       <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0BH325_1.jpg, 0BH325_1.png, 0BH325_2.png, 0BH325_3.png</t>
         </is>
@@ -4101,14 +4126,15 @@
         <v>10000</v>
       </c>
       <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0BH325183_1.png, 0BH325183_2.png</t>
         </is>
@@ -4151,14 +4177,15 @@
         <v>10000</v>
       </c>
       <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0BH325183 B_1.png, 0BH325183 B_2.png</t>
         </is>
@@ -4189,7 +4216,8 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Алюминиевый корпус фильтра DSG7 DQ500 — 0BH325183B
 Надёжный алюминиевый корпус фильтра, совместимый с 7-ступенчатой коробкой передач DSG DQ500 с мокрым сцеплением. Является лучшей альтернативой пластиковому варианту — отлично справляется с охлаждением и защитой масляного фильтра.
@@ -4209,9 +4237,9 @@
 Резиновое кольцо в комплекте</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0BH325183B_1.png, 0BH325183B_2.png, 0BH325183B_3.png</t>
         </is>
@@ -4242,7 +4270,8 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -4264,9 +4293,9 @@
 </t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -4297,7 +4326,8 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW ОРИГИНАЛЫ РАСХОДНИКИ Volkswagen
 В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.
@@ -4320,9 +4350,9 @@
 </t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -4365,14 +4395,15 @@
         <v>18000</v>
       </c>
       <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0am325025.png, 0am325025_1.png</t>
         </is>
@@ -4415,14 +4446,15 @@
         <v>5000</v>
       </c>
       <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0am325025D_1.png, 0am325025D_2.png</t>
         </is>
@@ -4465,14 +4497,15 @@
         <v>6000</v>
       </c>
       <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0am325025G_1.png, 0am325025G_2.png, 0am325025G_3.png</t>
         </is>
@@ -4511,18 +4544,19 @@
         <v>90000</v>
       </c>
       <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>#dq200 #мехатроник_dq200 #dsg7 #dsg7_dq200 #dsg7_0am_dq200 #0am325066ae #0am325066ac #0am325066 #dq200ремкомплект #0am325025 #0am325025d</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0am325025H-1.png, 0am325025H_1.jpg</t>
         </is>
@@ -4553,7 +4587,8 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)
 Описание товара
@@ -4577,9 +4612,9 @@
 </t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -4622,18 +4657,19 @@
         <v>150000</v>
       </c>
       <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0am325025HX_1.png, 0am325025HX_2.png</t>
         </is>
@@ -4676,14 +4712,15 @@
         <v>2000</v>
       </c>
       <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025P.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0am325025P_1.png, 0am325025P_2.png</t>
         </is>
@@ -4714,7 +4751,8 @@
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников (как на фото) Максимально профессиональное восстановление в заводских условиях + проверка на стенде = отличный результат и гарантия работоспособности.
 без электронной платы только гидравлика
@@ -4739,9 +4777,9 @@
 </t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -4784,18 +4822,19 @@
         <v>8000</v>
       </c>
       <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0am325025ae_1.png, 0am325025ae_2.png</t>
         </is>
@@ -4838,14 +4877,15 @@
         <v>6000</v>
       </c>
       <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>0am325025f_1.png</t>
         </is>
@@ -4888,14 +4928,15 @@
         <v>3500</v>
       </c>
       <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0am325025h.png, 0am325025h_1.png, 0am325025h_3.png, 0am325025h_4.png, 0am325025h_6.png</t>
         </is>
@@ -4938,18 +4979,19 @@
         <v>5000</v>
       </c>
       <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0am325025j_1.png, 0am325025j_2.png</t>
         </is>
@@ -4992,14 +5034,15 @@
         <v>2300</v>
       </c>
       <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>0am325025l.png, 0am325025l_1.png</t>
         </is>
@@ -5042,14 +5085,15 @@
         <v>12000</v>
       </c>
       <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0am325025m_1.png</t>
         </is>
@@ -5092,14 +5136,15 @@
         <v>12000</v>
       </c>
       <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>0am325025n_1.jpg, 0am325025n_1.png</t>
         </is>
@@ -5142,14 +5187,15 @@
         <v>1800</v>
       </c>
       <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0am325025q_1.png, 0am325025q_2.png</t>
         </is>
@@ -5192,14 +5238,15 @@
         <v>2500</v>
       </c>
       <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>0am325025r_1.png</t>
         </is>
@@ -5242,14 +5289,15 @@
         <v>6000</v>
       </c>
       <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025u.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>0am325025u_1.png</t>
         </is>
@@ -5288,18 +5336,19 @@
         <v>90000</v>
       </c>
       <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>#Мехатроникdsg7 #Мехатроникdq200</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0am325025x_1.jpg</t>
         </is>
@@ -5342,14 +5391,15 @@
         <v>6000</v>
       </c>
       <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025z.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>0am325025z.png</t>
         </is>
@@ -5380,7 +5430,8 @@
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Абсолютно новый мехатроник DSG7 DQ200 (0AM / 0CW) — гидравлическая часть
 В продаже полностью восстановленный до состояния нового мехатроник DSG7 DQ200 для коробок передач 0AM и 0CW. Узел собран с использованием новых оригинальных и OEM-компонентов, прошёл обязательную проверку и готов к установке.
@@ -5421,9 +5472,9 @@
 Капитальном ремонте коробки DQ200</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -5466,14 +5517,15 @@
         <v>2000</v>
       </c>
       <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025С.&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>0am325025С_1.png</t>
         </is>
@@ -5516,14 +5568,15 @@
         <v>2500</v>
       </c>
       <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>0am325066AC_1.png</t>
         </is>
@@ -5566,14 +5619,15 @@
         <v>2000</v>
       </c>
       <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>0am325066ad_1.jpg, 0am325066ad_1.png</t>
         </is>
@@ -5616,14 +5670,15 @@
         <v>10000</v>
       </c>
       <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>0am325066ae_1.png, 0am325066ae_4.png</t>
         </is>
@@ -5666,18 +5721,19 @@
         <v>5000</v>
       </c>
       <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>#dq200 #dsg7</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>0am325091e.png, 0am325091e_1.png</t>
         </is>
@@ -5716,18 +5772,19 @@
         <v>12000</v>
       </c>
       <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 длинных штока 101мм 0AM325091E усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091e. Проверить вес/габариты упаковки под комплект (больше, чем у одиночного штока).</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>0am325091e-set_1.png</t>
         </is>
@@ -5770,14 +5827,15 @@
         <v>5000</v>
       </c>
       <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>0am325091f.png, 0am325091f_1.png</t>
         </is>
@@ -5816,18 +5874,19 @@
         <v>12000</v>
       </c>
       <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 коротких штока 99мм 0AM325091F усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091f. Проверить вес/габариты упаковки под комплект.</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>0am325091f-set_1.png</t>
         </is>
@@ -5870,14 +5929,15 @@
         <v>4000</v>
       </c>
       <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>0am325477ae_1.png, 0am325477ae_2.png, 0am325477ae_3.png, 0am325477ae_4.png</t>
         </is>
@@ -5916,14 +5976,15 @@
         <v>15000</v>
       </c>
       <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>0ambset_1.png, 0ambset_2.png</t>
         </is>
@@ -5962,18 +6023,19 @@
         <v>0</v>
       </c>
       <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>#Прокладкаdsg7dq200</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>0cw0am_1.jpg, 0cw0am_1.png</t>
         </is>
@@ -6012,18 +6074,19 @@
         <v>25000</v>
       </c>
       <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>#Прокладкиdq200</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>0cw0am325025-2.png, 0cw0am325025.png, 0cw0am325025_1.png</t>
         </is>
@@ -6062,18 +6125,19 @@
         <v>1500</v>
       </c>
       <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>#Прокладкаdq200dsg</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200_1.jpg</t>
         </is>
@@ -6112,18 +6176,19 @@
         <v>2000</v>
       </c>
       <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>0cw325025h_1.png, 0cw325025h_2.png, 0cw325025h_3.png, 0cw325025h_4.png</t>
         </is>
@@ -6162,14 +6227,15 @@
         <v>2500</v>
       </c>
       <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>0сц_1.png, 0сц_2.png, 0сц_3.png, 0сц_4.png, 0сц_5.png, 0сц_6.png, 0сц_7.png</t>
         </is>
@@ -6212,14 +6278,15 @@
         <v>1500</v>
       </c>
       <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>122390AK-AF_1.jpg, 122390AK-AF_1.png</t>
         </is>
@@ -6262,14 +6329,15 @@
         <v>2500</v>
       </c>
       <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>122390AKAF_1.png</t>
         </is>
@@ -6312,14 +6380,15 @@
         <v>2500</v>
       </c>
       <c r="J64" s="2" t="n"/>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>123014‑AF_1.png, 123014‑AF_2.png</t>
         </is>
@@ -6362,18 +6431,19 @@
         <v>80000</v>
       </c>
       <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>#гидроблокjf011e</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>31705-1XF0C_1.jpg</t>
         </is>
@@ -6404,7 +6474,8 @@
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
       <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E Старое поколение для вариатора CVT RE0F10A. Восстанавливает давление масла и стабильную работу трансмиссии. Прямая замена штатного узла без доработок.
 Гидроблок вариатора JF011E Старое поколение — управляющий узел CVT-коробки, отвечающий за распределение давления масла и работу соленоидов. Применяется в вариаторах RE0F10A и устанавливается на автомобили Nissan, Mitsubishi, Renault и Jeep.
@@ -6432,9 +6503,9 @@
 гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi ремонт вариатора jf011e</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -6477,18 +6548,19 @@
         <v>80000</v>
       </c>
       <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>31705-X428B_1.png, 31705-X428B_2.png, 31705-X428B_3.png</t>
         </is>
@@ -6531,14 +6603,15 @@
         <v>80000</v>
       </c>
       <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>317053TX0C_1.png</t>
         </is>
@@ -6581,14 +6654,15 @@
         <v>2000</v>
       </c>
       <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>55565480_1.png</t>
         </is>
@@ -6627,18 +6701,19 @@
         <v>6000</v>
       </c>
       <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>Образец — 0AM325473 (Соленоиды мехатроника DSG7 DQ200 0AM 0CW), по твоему решению: категория/характеристики 'соленоидов' в Ozon, скорее всего, достаточно общие, чтобы не заводить отдельно через кабинет. Категорию/атрибуты после создания стоит один раз проверить в кабинете Ozon — если что-то не подойдёт (например размеры/вес явно другие для 6T30), поправим вручную.</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>6t30_1.png</t>
         </is>
@@ -6669,15 +6744,16 @@
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
       <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
 Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -6708,7 +6784,8 @@
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
       <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>Комплект корпуса масляного фильтра с фильтром для роботизированной коробки передач DSG7 DQ500 (0BH).
 Подходит для автомобилей VAG с 7-ступенчатой мокрой DSG DQ500.
@@ -6716,9 +6793,9 @@
 Рекомендуется при обслуживании и ремонте DSG 7 DQ500.</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
@@ -6757,14 +6834,15 @@
         <v>8000</v>
       </c>
       <c r="J73" s="2" t="n"/>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
-      <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>DQ500-a-1.png, DQ500_1.png, DQ500_3.png, DQ500_a-2.png, dq500.png</t>
         </is>
@@ -6803,18 +6881,19 @@
         <v>1500</v>
       </c>
       <c r="J74" s="2" t="n"/>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>#Прокладкаdq200</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Dq200dsg7_1.jpg</t>
         </is>
@@ -6853,14 +6932,15 @@
         <v>12000</v>
       </c>
       <c r="J75" s="2" t="n"/>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>Dq200dsg70am0cw_1.jpg</t>
         </is>
@@ -6899,14 +6979,15 @@
         <v>6000</v>
       </c>
       <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>Dq500_1.jpg, Dq500_2.png</t>
         </is>
@@ -6945,18 +7026,19 @@
         <v>6000</v>
       </c>
       <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>#корпусмасляногофильтраEA888</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>EA888_1.png</t>
         </is>
@@ -6995,14 +7077,15 @@
         <v>10000</v>
       </c>
       <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>EA888gen3_1.jpg</t>
         </is>
@@ -7041,14 +7124,15 @@
         <v>3500</v>
       </c>
       <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
         </is>
@@ -7087,14 +7171,15 @@
         <v>0</v>
       </c>
       <c r="J80" s="2" t="n"/>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>TEST001_2.jpg</t>
         </is>
@@ -7124,17 +7209,18 @@
       </c>
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>Тестовая карточка для проверки автоматизации</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>TESTWB001_2.jpg</t>
         </is>
@@ -7177,14 +7263,15 @@
         <v>1500</v>
       </c>
       <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>WHT001922_1.png</t>
         </is>
@@ -7223,18 +7310,19 @@
         <v>2500</v>
       </c>
       <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>filtr-setka-0b5-orig_1.png</t>
         </is>
@@ -7273,18 +7361,19 @@
         <v>12000</v>
       </c>
       <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
         </is>
       </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>gidroakkumulyator-orig_1.png, gidroakkumulyator-orig_2.png, gidroakkumulyator-orig_3.png</t>
         </is>
@@ -7327,14 +7416,15 @@
         <v>15000</v>
       </c>
       <c r="J85" s="2" t="n"/>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="n"/>
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>jf011e_1.jpg</t>
         </is>
@@ -7373,18 +7463,19 @@
         <v>1500</v>
       </c>
       <c r="J86" s="2" t="n"/>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>klipsy-shtokov-2sht_1.png</t>
         </is>
@@ -7423,18 +7514,19 @@
         <v>6000</v>
       </c>
       <c r="J87" s="2" t="n"/>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="n"/>
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>Найден через next.png/next-2.png ещё раньше. Отдельный корпус фильтра 0BH325159 — сейчас в каталоге есть только 0BH325183B (сам фильтр) и наборы DQ500/DQ500-a/Dq500 (корпус+фильтр вместе). Образец — 0BH325183B.</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
         </is>
@@ -7473,14 +7565,15 @@
         <v>1500</v>
       </c>
       <c r="J88" s="2" t="n"/>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>nakladki-pedali_1.png, nakladki-pedali_2.png</t>
         </is>
@@ -7519,18 +7612,19 @@
         <v>4000</v>
       </c>
       <c r="J89" s="2" t="n"/>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K89" s="2" t="n"/>
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Комплект 2 шт — в отличие от одиночной планки 0am325477ae (1 шт).</t>
         </is>
       </c>
-      <c r="N89" s="2" t="inlineStr">
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>planka-solenoid-2sht_1.png</t>
         </is>
@@ -7569,18 +7663,19 @@
         <v>2000</v>
       </c>
       <c r="J90" s="2" t="n"/>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="K90" s="2" t="n"/>
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только пластины на соленоиды, оригинал VW, без сепараторной пластины (в отличие от связки 0am325025j).</t>
         </is>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>plastiny-solenoid-orig_1.png</t>
         </is>
@@ -7619,18 +7714,19 @@
         <v>12000</v>
       </c>
       <c r="J91" s="2" t="n"/>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K91" s="2" t="n"/>
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>plita-filtr_1.png</t>
         </is>
@@ -7669,18 +7765,19 @@
         <v>12000</v>
       </c>
       <c r="J92" s="2" t="n"/>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="K92" s="2" t="n"/>
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki_1.png</t>
         </is>
@@ -7719,18 +7816,19 @@
         <v>13000</v>
       </c>
       <c r="J93" s="2" t="n"/>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="K93" s="2" t="n"/>
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="O93" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki-orig_1.png</t>
         </is>
@@ -7769,18 +7867,19 @@
         <v>13000</v>
       </c>
       <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="K94" s="2" t="n"/>
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki-sal_1.png</t>
         </is>
@@ -7819,18 +7918,19 @@
         <v>12000</v>
       </c>
       <c r="J95" s="2" t="n"/>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K95" s="2" t="n"/>
+      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr">
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
-      <c r="N95" s="2" t="inlineStr">
+      <c r="O95" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
         </is>
@@ -7869,14 +7969,15 @@
         <v>13500</v>
       </c>
       <c r="J96" s="2" t="n"/>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="K96" s="2" t="n"/>
+      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
-      <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>plita-pylniki-salniki-orig_1.png</t>
         </is>
@@ -7915,18 +8016,19 @@
         <v>1500</v>
       </c>
       <c r="J97" s="2" t="n"/>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K97" s="2" t="n"/>
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4 (2 фото — 'подшипник' и 'подшипники', похоже один и тот же товар). Совсем новая категория, аналогов в каталоге нет. Образец взял 0ambset (тоже подшипники) — категория/атрибуты нужно перепроверить вручную в кабинете Ozon.</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>podshipnik-vilki-6_1.png, podshipnik-vilki-6_2.png</t>
         </is>
@@ -7965,18 +8067,19 @@
         <v>6500</v>
       </c>
       <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="K98" s="2" t="n"/>
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>Цена — грубая оценка Клода (аналогичного готового комплекта именно с усиленными поршнями в файле раньше не было, ориентировался на цену поршня по отдельности + похожий комплект с сальниками вместо поршней) — проверьте и поправьте сами.</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>porshni-usil-pylniki-kryshki_1.png</t>
         </is>
@@ -8015,18 +8118,19 @@
         <v>3000</v>
       </c>
       <c r="J99" s="2" t="n"/>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K99" s="2" t="n"/>
+      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только пыльники (без сальников и крышек), оригинал VAG.</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>pylniki-shtokov-orig_1.png</t>
         </is>
@@ -8065,18 +8169,19 @@
         <v>4000</v>
       </c>
       <c r="J100" s="2" t="n"/>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K100" s="2" t="n"/>
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Оригинал VAG версия существующего аналогового ремкомплекта 0am325025G. Уточнить у поставщика реальную оригинальность/цену закупки.</t>
         </is>
       </c>
-      <c r="N100" s="2" t="inlineStr">
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>remkomplekt-shtokov-orig_1.png</t>
         </is>
@@ -8115,18 +8220,19 @@
         <v>2500</v>
       </c>
       <c r="J101" s="2" t="n"/>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K101" s="2" t="n"/>
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr">
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 3 и 5 (2 фото). Оригинал VAG версия обычного аналогового сальника 0AM325413A.</t>
         </is>
       </c>
-      <c r="N101" s="2" t="inlineStr">
+      <c r="O101" s="2" t="inlineStr">
         <is>
           <t>salnik-shtoka-orig_1.png, salnik-shtoka-orig_2.png</t>
         </is>
@@ -8165,18 +8271,19 @@
         <v>4500</v>
       </c>
       <c r="J102" s="2" t="n"/>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K102" s="2" t="n"/>
+      <c r="L102" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 1 и 3 (2 фото). Премиум-вариант обычного сальника толкателя 0AM325413A — алюминиевый корпус с гальваническим покрытием.</t>
         </is>
       </c>
-      <c r="N102" s="2" t="inlineStr">
+      <c r="O102" s="2" t="inlineStr">
         <is>
           <t>salnik-tolkatelya-alum_1.png, salnik-tolkatelya-alum_2.png</t>
         </is>
@@ -8215,18 +8322,19 @@
         <v>2800</v>
       </c>
       <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K103" s="2" t="n"/>
+      <c r="L103" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Только сальники штоков (без пыльников/крышек), комплект 2 шт, аналог (не оригинал).</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>salniki-shtokov-2sht_1.png</t>
         </is>
@@ -8265,18 +8373,19 @@
         <v>3000</v>
       </c>
       <c r="J104" s="2" t="n"/>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="K104" s="2" t="n"/>
+      <c r="L104" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr">
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только сальники (без пыльников и крышек), оригинал VAG.</t>
         </is>
       </c>
-      <c r="N104" s="2" t="inlineStr">
+      <c r="O104" s="2" t="inlineStr">
         <is>
           <t>salniki-shtokov-orig_1.png</t>
         </is>
@@ -8315,18 +8424,19 @@
         <v>3000</v>
       </c>
       <c r="J105" s="2" t="n"/>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K105" s="2" t="n"/>
+      <c r="L105" s="2" t="inlineStr">
         <is>
           <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr">
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
         <is>
           <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
         </is>
       </c>
-      <c r="N105" s="2" t="inlineStr">
+      <c r="O105" s="2" t="inlineStr">
         <is>
           <t>salniki-tolkatelya-4sht_1.png, salniki-tolkatelya-4sht_2.png</t>
         </is>
@@ -8365,18 +8475,19 @@
         <v>1700</v>
       </c>
       <c r="J106" s="2" t="n"/>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="K106" s="2" t="n"/>
+      <c r="L106" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr">
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (та же формулировка, что в seo_keywords.xlsx). Образец 0AM325413A — тоже сальник той же линейки, категория/атрибуты должны подойти.</t>
         </is>
       </c>
-      <c r="N106" s="2" t="inlineStr">
+      <c r="O106" s="2" t="inlineStr">
         <is>
           <t>salnikprivod-l_1.png</t>
         </is>
@@ -8415,18 +8526,19 @@
         <v>1700</v>
       </c>
       <c r="J107" s="2" t="n"/>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="K107" s="2" t="n"/>
+      <c r="L107" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики. Образец 0AM325413A — тоже сальник той же линейки.</t>
         </is>
       </c>
-      <c r="N107" s="2" t="inlineStr">
+      <c r="O107" s="2" t="inlineStr">
         <is>
           <t>salnikprivod-r_1.png</t>
         </is>
@@ -8465,18 +8577,19 @@
         <v>1700</v>
       </c>
       <c r="J108" s="2" t="n"/>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K108" s="2" t="n"/>
+      <c r="L108" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (сальник входного вала).</t>
         </is>
       </c>
-      <c r="N108" s="2" t="inlineStr">
+      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>salnikvhod_1.png</t>
         </is>
@@ -8515,18 +8628,19 @@
         <v>1700</v>
       </c>
       <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="K109" s="2" t="n"/>
+      <c r="L109" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК — в собранной семантике есть 'сальник первичного вала' и 'сальник входного вала', но не 'выходного'. Уточни, это точно отдельная деталь (выходной/вторичный вал) или это то же самое, что 'первичный вал' у вас в терминологии?</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="O109" s="2" t="inlineStr">
         <is>
           <t>salnikvihod_1.png</t>
         </is>
@@ -8565,18 +8679,19 @@
         <v>3500</v>
       </c>
       <c r="J110" s="2" t="n"/>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Новая деталь, аналогов в каталоге нет. Образец — плита 0am325066ae, проверить категорию/атрибуты вручную.</t>
         </is>
       </c>
-      <c r="N110" s="2" t="inlineStr">
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>stalnaya-vstavka-plity_1.png</t>
         </is>
@@ -8615,18 +8730,19 @@
         <v>10000</v>
       </c>
       <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="K111" s="2" t="n"/>
+      <c r="L111" s="2" t="inlineStr">
         <is>
           <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
-      <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr">
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Полный комплект на все 4 позиции мехатроника — в отличие от одиночного толкателя 0am325066AC. Пересчитать вес/габариты.</t>
         </is>
       </c>
-      <c r="N111" s="2" t="inlineStr">
+      <c r="O111" s="2" t="inlineStr">
         <is>
           <t>tolkateli-4-salniki-4_1.png</t>
         </is>
@@ -8665,18 +8781,19 @@
         <v>12000</v>
       </c>
       <c r="J112" s="2" t="n"/>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K112" s="2" t="n"/>
+      <c r="L112" s="2" t="inlineStr">
         <is>
           <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
         </is>
       </c>
-      <c r="N112" s="2" t="inlineStr">
+      <c r="O112" s="2" t="inlineStr">
         <is>
           <t>tolkateli-salniki-alum-komplekt_1.png</t>
         </is>
@@ -8715,18 +8832,19 @@
         <v>7000</v>
       </c>
       <c r="J113" s="2" t="n"/>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K113" s="2" t="n"/>
+      <c r="L113" s="2" t="inlineStr">
         <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только втулки (без штоков), комплект 2 шт — в отличие от одиночной втулки 0am325025D.</t>
         </is>
       </c>
-      <c r="N113" s="2" t="inlineStr">
+      <c r="O113" s="2" t="inlineStr">
         <is>
           <t>vtulki-shtokov-2sht_1.png</t>
         </is>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -3302,7 +3302,9 @@
       <c r="I5" s="2" t="n">
         <v>145000</v>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -5771,7 +5773,9 @@
       <c r="I52" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J52" s="2" t="n"/>
+      <c r="J52" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -5873,7 +5877,9 @@
       <c r="I54" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J54" s="2" t="n"/>
+      <c r="J54" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -6700,7 +6706,9 @@
       <c r="I70" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J70" s="2" t="n"/>
+      <c r="J70" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -7309,7 +7317,9 @@
       <c r="I83" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J83" s="2" t="n"/>
+      <c r="J83" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K83" s="2" t="n"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -7360,7 +7370,9 @@
       <c r="I84" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J84" s="2" t="n"/>
+      <c r="J84" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -7462,7 +7474,9 @@
       <c r="I86" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J86" s="2" t="n"/>
+      <c r="J86" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -7513,7 +7527,9 @@
       <c r="I87" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J87" s="2" t="n"/>
+      <c r="J87" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -7611,7 +7627,9 @@
       <c r="I89" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="J89" s="2" t="n"/>
+      <c r="J89" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -7662,7 +7680,9 @@
       <c r="I90" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="J90" s="2" t="n"/>
+      <c r="J90" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
@@ -7713,7 +7733,9 @@
       <c r="I91" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J91" s="2" t="n"/>
+      <c r="J91" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -7764,7 +7786,9 @@
       <c r="I92" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J92" s="2" t="n"/>
+      <c r="J92" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -7815,7 +7839,9 @@
       <c r="I93" s="2" t="n">
         <v>13000</v>
       </c>
-      <c r="J93" s="2" t="n"/>
+      <c r="J93" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
@@ -7866,7 +7892,9 @@
       <c r="I94" s="2" t="n">
         <v>13000</v>
       </c>
-      <c r="J94" s="2" t="n"/>
+      <c r="J94" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
@@ -7917,7 +7945,9 @@
       <c r="I95" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J95" s="2" t="n"/>
+      <c r="J95" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
@@ -7968,7 +7998,9 @@
       <c r="I96" s="2" t="n">
         <v>13500</v>
       </c>
-      <c r="J96" s="2" t="n"/>
+      <c r="J96" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
@@ -8015,7 +8047,9 @@
       <c r="I97" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J97" s="2" t="n"/>
+      <c r="J97" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -8066,7 +8100,9 @@
       <c r="I98" s="2" t="n">
         <v>6500</v>
       </c>
-      <c r="J98" s="2" t="n"/>
+      <c r="J98" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K98" s="2" t="n"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
@@ -8117,7 +8153,9 @@
       <c r="I99" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="J99" s="2" t="n"/>
+      <c r="J99" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
@@ -8168,7 +8206,9 @@
       <c r="I100" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="J100" s="2" t="n"/>
+      <c r="J100" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
@@ -8219,7 +8259,9 @@
       <c r="I101" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J101" s="2" t="n"/>
+      <c r="J101" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -8270,7 +8312,9 @@
       <c r="I102" s="2" t="n">
         <v>4500</v>
       </c>
-      <c r="J102" s="2" t="n"/>
+      <c r="J102" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
@@ -8321,7 +8365,9 @@
       <c r="I103" s="2" t="n">
         <v>2800</v>
       </c>
-      <c r="J103" s="2" t="n"/>
+      <c r="J103" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
@@ -8372,7 +8418,9 @@
       <c r="I104" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="J104" s="2" t="n"/>
+      <c r="J104" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
@@ -8423,7 +8471,9 @@
       <c r="I105" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="J105" s="2" t="n"/>
+      <c r="J105" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
@@ -8474,7 +8524,9 @@
       <c r="I106" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="J106" s="2" t="n"/>
+      <c r="J106" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K106" s="2" t="n"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
@@ -8525,7 +8577,9 @@
       <c r="I107" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="J107" s="2" t="n"/>
+      <c r="J107" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
@@ -8576,7 +8630,9 @@
       <c r="I108" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="J108" s="2" t="n"/>
+      <c r="J108" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K108" s="2" t="n"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
@@ -8627,7 +8683,9 @@
       <c r="I109" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="J109" s="2" t="n"/>
+      <c r="J109" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
@@ -8678,7 +8736,9 @@
       <c r="I110" s="2" t="n">
         <v>3500</v>
       </c>
-      <c r="J110" s="2" t="n"/>
+      <c r="J110" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
@@ -8729,7 +8789,9 @@
       <c r="I111" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="J111" s="2" t="n"/>
+      <c r="J111" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
@@ -8780,7 +8842,9 @@
       <c r="I112" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J112" s="2" t="n"/>
+      <c r="J112" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
@@ -8831,7 +8895,9 @@
       <c r="I113" s="2" t="n">
         <v>7000</v>
       </c>
-      <c r="J113" s="2" t="n"/>
+      <c r="J113" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="inlineStr">
         <is>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -3157,7 +3157,9 @@
       <c r="I2" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J2" s="2" t="n"/>
+      <c r="J2" s="2" t="n">
+        <v>90</v>
+      </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -3204,7 +3206,9 @@
       <c r="I3" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -3255,7 +3259,9 @@
       <c r="I4" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="2" t="n">
+        <v>95</v>
+      </c>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -3359,7 +3365,9 @@
       <c r="I6" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="2" t="n">
+        <v>87</v>
+      </c>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -3410,7 +3418,9 @@
       <c r="I7" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -3461,7 +3471,9 @@
       <c r="I8" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -3566,7 +3578,9 @@
       <c r="I10" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -3617,7 +3631,9 @@
       <c r="I11" s="2" t="n">
         <v>4500</v>
       </c>
-      <c r="J11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>49</v>
+      </c>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -3668,7 +3684,9 @@
       <c r="I12" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J12" s="2" t="n"/>
+      <c r="J12" s="2" t="n">
+        <v>83</v>
+      </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -3719,7 +3737,9 @@
       <c r="I13" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="2" t="n">
+        <v>87</v>
+      </c>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -3770,7 +3790,9 @@
       <c r="I14" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="2" t="n">
+        <v>51</v>
+      </c>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -3825,7 +3847,9 @@
       <c r="I15" s="2" t="n">
         <v>3500</v>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="2" t="n">
+        <v>35</v>
+      </c>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -3876,7 +3900,9 @@
       <c r="I16" s="2" t="n">
         <v>15000</v>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -3927,7 +3953,9 @@
       <c r="I17" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="2" t="n">
+        <v>28</v>
+      </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -3978,7 +4006,9 @@
       <c r="I18" s="2" t="n">
         <v>80000</v>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -4029,7 +4059,9 @@
       <c r="I19" s="2" t="n">
         <v>4500</v>
       </c>
-      <c r="J19" s="2" t="n"/>
+      <c r="J19" s="2" t="n">
+        <v>51</v>
+      </c>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -4076,7 +4108,9 @@
       <c r="I20" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -4127,7 +4161,9 @@
       <c r="I21" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="J21" s="2" t="n"/>
+      <c r="J21" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -4178,7 +4214,9 @@
       <c r="I22" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="J22" s="2" t="n"/>
+      <c r="J22" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -4396,7 +4434,9 @@
       <c r="I26" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="J26" s="2" t="n"/>
+      <c r="J26" s="2" t="n">
+        <v>25</v>
+      </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -4447,7 +4487,9 @@
       <c r="I27" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="J27" s="2" t="n"/>
+      <c r="J27" s="2" t="n">
+        <v>74</v>
+      </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -4498,7 +4540,9 @@
       <c r="I28" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J28" s="2" t="n"/>
+      <c r="J28" s="2" t="n">
+        <v>93</v>
+      </c>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -4545,7 +4589,9 @@
       <c r="I29" s="2" t="n">
         <v>90000</v>
       </c>
-      <c r="J29" s="2" t="n"/>
+      <c r="J29" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -4658,7 +4704,9 @@
       <c r="I31" s="2" t="n">
         <v>150000</v>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -4713,7 +4761,9 @@
       <c r="I32" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="J32" s="2" t="n"/>
+      <c r="J32" s="2" t="n">
+        <v>69</v>
+      </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -4823,7 +4873,9 @@
       <c r="I34" s="2" t="n">
         <v>8000</v>
       </c>
-      <c r="J34" s="2" t="n"/>
+      <c r="J34" s="2" t="n">
+        <v>31</v>
+      </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -4878,7 +4930,9 @@
       <c r="I35" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J35" s="2" t="n"/>
+      <c r="J35" s="2" t="n">
+        <v>43</v>
+      </c>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -4929,7 +4983,9 @@
       <c r="I36" s="2" t="n">
         <v>3500</v>
       </c>
-      <c r="J36" s="2" t="n"/>
+      <c r="J36" s="2" t="n">
+        <v>93</v>
+      </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -4980,7 +5036,9 @@
       <c r="I37" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="J37" s="2" t="n"/>
+      <c r="J37" s="2" t="n">
+        <v>88</v>
+      </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -5035,7 +5093,9 @@
       <c r="I38" s="2" t="n">
         <v>2300</v>
       </c>
-      <c r="J38" s="2" t="n"/>
+      <c r="J38" s="2" t="n">
+        <v>86</v>
+      </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -5086,7 +5146,9 @@
       <c r="I39" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J39" s="2" t="n"/>
+      <c r="J39" s="2" t="n">
+        <v>74</v>
+      </c>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -5137,7 +5199,9 @@
       <c r="I40" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J40" s="2" t="n"/>
+      <c r="J40" s="2" t="n">
+        <v>25</v>
+      </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -5188,7 +5252,9 @@
       <c r="I41" s="2" t="n">
         <v>1800</v>
       </c>
-      <c r="J41" s="2" t="n"/>
+      <c r="J41" s="2" t="n">
+        <v>53</v>
+      </c>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -5239,7 +5305,9 @@
       <c r="I42" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J42" s="2" t="n"/>
+      <c r="J42" s="2" t="n">
+        <v>36</v>
+      </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -5290,7 +5358,9 @@
       <c r="I43" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J43" s="2" t="n"/>
+      <c r="J43" s="2" t="n">
+        <v>82</v>
+      </c>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -5337,7 +5407,9 @@
       <c r="I44" s="2" t="n">
         <v>90000</v>
       </c>
-      <c r="J44" s="2" t="n"/>
+      <c r="J44" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -5392,7 +5464,9 @@
       <c r="I45" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J45" s="2" t="n"/>
+      <c r="J45" s="2" t="n">
+        <v>47</v>
+      </c>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -5518,7 +5592,9 @@
       <c r="I47" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="J47" s="2" t="n"/>
+      <c r="J47" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -5569,7 +5645,9 @@
       <c r="I48" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J48" s="2" t="n"/>
+      <c r="J48" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -5620,7 +5698,9 @@
       <c r="I49" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="J49" s="2" t="n"/>
+      <c r="J49" s="2" t="n">
+        <v>21</v>
+      </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -5671,7 +5751,9 @@
       <c r="I50" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="J50" s="2" t="n"/>
+      <c r="J50" s="2" t="n">
+        <v>49</v>
+      </c>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -5722,7 +5804,9 @@
       <c r="I51" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="J51" s="2" t="n"/>
+      <c r="J51" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5914,9 @@
       <c r="I53" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="J53" s="2" t="n"/>
+      <c r="J53" s="2" t="n">
+        <v>29</v>
+      </c>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
@@ -5934,7 +6020,9 @@
       <c r="I55" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="J55" s="2" t="n"/>
+      <c r="J55" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
@@ -5981,7 +6069,9 @@
       <c r="I56" s="2" t="n">
         <v>15000</v>
       </c>
-      <c r="J56" s="2" t="n"/>
+      <c r="J56" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
@@ -6028,7 +6118,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="2" t="n"/>
+      <c r="J57" s="2" t="n">
+        <v>49</v>
+      </c>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
@@ -6079,7 +6171,9 @@
       <c r="I58" s="2" t="n">
         <v>25000</v>
       </c>
-      <c r="J58" s="2" t="n"/>
+      <c r="J58" s="2" t="n">
+        <v>80</v>
+      </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -6130,7 +6224,9 @@
       <c r="I59" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J59" s="2" t="n"/>
+      <c r="J59" s="2" t="n">
+        <v>49</v>
+      </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -6181,7 +6277,9 @@
       <c r="I60" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="J60" s="2" t="n"/>
+      <c r="J60" s="2" t="n">
+        <v>53</v>
+      </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
@@ -6232,7 +6330,9 @@
       <c r="I61" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J61" s="2" t="n"/>
+      <c r="J61" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
@@ -6283,7 +6383,9 @@
       <c r="I62" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J62" s="2" t="n"/>
+      <c r="J62" s="2" t="n">
+        <v>32</v>
+      </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
@@ -6334,7 +6436,9 @@
       <c r="I63" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J63" s="2" t="n"/>
+      <c r="J63" s="2" t="n">
+        <v>36</v>
+      </c>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -6385,7 +6489,9 @@
       <c r="I64" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J64" s="2" t="n"/>
+      <c r="J64" s="2" t="n">
+        <v>28</v>
+      </c>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
@@ -6436,7 +6542,9 @@
       <c r="I65" s="2" t="n">
         <v>80000</v>
       </c>
-      <c r="J65" s="2" t="n"/>
+      <c r="J65" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -6553,7 +6661,9 @@
       <c r="I67" s="2" t="n">
         <v>80000</v>
       </c>
-      <c r="J67" s="2" t="n"/>
+      <c r="J67" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
@@ -6608,7 +6718,9 @@
       <c r="I68" s="2" t="n">
         <v>80000</v>
       </c>
-      <c r="J68" s="2" t="n"/>
+      <c r="J68" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
@@ -6659,7 +6771,9 @@
       <c r="I69" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="J69" s="2" t="n"/>
+      <c r="J69" s="2" t="n">
+        <v>37</v>
+      </c>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -6841,7 +6955,9 @@
       <c r="I73" s="2" t="n">
         <v>8000</v>
       </c>
-      <c r="J73" s="2" t="n"/>
+      <c r="J73" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
@@ -6888,7 +7004,9 @@
       <c r="I74" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J74" s="2" t="n"/>
+      <c r="J74" s="2" t="n">
+        <v>44</v>
+      </c>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
@@ -6939,7 +7057,9 @@
       <c r="I75" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J75" s="2" t="n"/>
+      <c r="J75" s="2" t="n">
+        <v>77</v>
+      </c>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
@@ -6986,7 +7106,9 @@
       <c r="I76" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J76" s="2" t="n"/>
+      <c r="J76" s="2" t="n">
+        <v>30</v>
+      </c>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
@@ -7033,7 +7155,9 @@
       <c r="I77" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J77" s="2" t="n"/>
+      <c r="J77" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -7084,7 +7208,9 @@
       <c r="I78" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="2" t="n">
+        <v>30</v>
+      </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -7131,7 +7257,9 @@
       <c r="I79" s="2" t="n">
         <v>3500</v>
       </c>
-      <c r="J79" s="2" t="n"/>
+      <c r="J79" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -7178,7 +7306,9 @@
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="2" t="n"/>
+      <c r="J80" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -7270,7 +7400,9 @@
       <c r="I82" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J82" s="2" t="n"/>
+      <c r="J82" s="2" t="n">
+        <v>93</v>
+      </c>
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -7427,7 +7559,9 @@
       <c r="I85" s="2" t="n">
         <v>15000</v>
       </c>
-      <c r="J85" s="2" t="n"/>
+      <c r="J85" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
@@ -7580,7 +7714,9 @@
       <c r="I88" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J88" s="2" t="n"/>
+      <c r="J88" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="inlineStr">
         <is>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -178,6 +178,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -203,6 +206,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -228,6 +234,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -253,6 +262,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -278,6 +290,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -303,6 +318,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -328,6 +346,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -353,6 +374,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -378,6 +402,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -403,6 +430,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -428,6 +458,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -453,6 +486,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -478,6 +514,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -503,6 +542,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -528,6 +570,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -553,6 +598,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -578,6 +626,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -603,6 +654,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -628,6 +682,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -653,6 +710,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -678,6 +738,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -703,6 +766,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -728,6 +794,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -753,6 +822,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -778,6 +850,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -803,6 +878,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -828,6 +906,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -853,6 +934,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -878,6 +962,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -903,6 +990,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -928,6 +1018,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -953,6 +1046,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -978,6 +1074,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1003,6 +1102,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1028,6 +1130,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1053,6 +1158,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1078,6 +1186,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1103,6 +1214,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1128,6 +1242,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1153,6 +1270,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1178,6 +1298,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1203,6 +1326,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1228,6 +1354,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1253,6 +1382,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1278,6 +1410,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1303,6 +1438,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1328,6 +1466,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1353,6 +1494,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1378,6 +1522,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1403,6 +1550,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1428,6 +1578,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1453,6 +1606,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1478,6 +1634,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1503,6 +1662,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1528,6 +1690,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1553,6 +1718,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1578,6 +1746,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1603,6 +1774,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1628,6 +1802,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1653,6 +1830,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1678,6 +1858,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1703,6 +1886,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1728,6 +1914,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1753,6 +1942,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1778,6 +1970,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1803,6 +1998,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1828,6 +2026,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1853,6 +2054,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1878,6 +2082,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1903,6 +2110,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1928,6 +2138,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1953,6 +2166,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1978,6 +2194,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2003,6 +2222,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2028,6 +2250,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2053,6 +2278,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2078,6 +2306,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2103,6 +2334,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2128,6 +2362,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2153,6 +2390,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2178,6 +2418,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2203,6 +2446,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2228,6 +2474,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2253,6 +2502,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2278,6 +2530,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2303,6 +2558,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2328,6 +2586,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2353,6 +2614,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2378,6 +2642,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2403,6 +2670,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2428,6 +2698,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2453,6 +2726,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2478,6 +2754,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2503,6 +2782,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2528,6 +2810,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2553,6 +2838,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2578,6 +2866,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2603,6 +2894,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2628,6 +2922,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2653,6 +2950,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2678,6 +2978,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2703,6 +3006,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2728,6 +3034,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4114,10 +4423,14 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -178,9 +178,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -206,9 +203,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -234,9 +228,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -262,9 +253,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -290,9 +278,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -318,9 +303,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -346,9 +328,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -374,9 +353,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -402,9 +378,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -430,9 +403,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -458,9 +428,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -486,9 +453,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -514,9 +478,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -542,9 +503,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -570,9 +528,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -598,9 +553,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -626,9 +578,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -654,9 +603,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -682,9 +628,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -710,9 +653,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -738,9 +678,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -766,9 +703,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -794,9 +728,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -822,9 +753,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -850,9 +778,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -878,9 +803,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -906,9 +828,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -934,9 +853,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -962,9 +878,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -990,9 +903,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1018,9 +928,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1046,9 +953,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1074,9 +978,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1102,9 +1003,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1130,9 +1028,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1158,9 +1053,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1186,9 +1078,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1214,9 +1103,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1242,9 +1128,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1270,9 +1153,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1298,9 +1178,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1326,9 +1203,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1354,9 +1228,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1382,9 +1253,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1410,9 +1278,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1438,9 +1303,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1466,9 +1328,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1494,9 +1353,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1522,9 +1378,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1550,9 +1403,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1578,9 +1428,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1606,9 +1453,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1634,9 +1478,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1662,9 +1503,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1690,9 +1528,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1718,9 +1553,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1746,9 +1578,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1774,9 +1603,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1802,9 +1628,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1830,9 +1653,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1858,9 +1678,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1886,9 +1703,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1914,9 +1728,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1942,9 +1753,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1970,9 +1778,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1998,9 +1803,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2026,9 +1828,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2054,9 +1853,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2082,9 +1878,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2110,9 +1903,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2138,9 +1928,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2166,9 +1953,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2194,9 +1978,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2222,9 +2003,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2250,9 +2028,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2278,9 +2053,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2306,9 +2078,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2334,9 +2103,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2362,9 +2128,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2390,9 +2153,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2418,9 +2178,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2446,9 +2203,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2474,9 +2228,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2502,18 +2253,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>94</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2530,18 +2278,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>95</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2558,18 +2303,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>96</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2586,18 +2328,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>97</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2614,18 +2353,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>98</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2642,18 +2378,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>99</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2670,18 +2403,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>100</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2698,18 +2428,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>101</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2726,18 +2453,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>102</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2754,18 +2478,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>103</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2782,18 +2503,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>104</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2810,18 +2528,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>105</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2838,18 +2553,15 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>106</row>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2866,177 +2578,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>107</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>110</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>111</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="102" name="Image 102" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="103" name="Image 103" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -8153,7 +7694,7 @@
     <row r="91" ht="78" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -8168,16 +7709,16 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="I91" s="2" t="n">
         <v>12000</v>
@@ -8188,25 +7729,25 @@
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
+          <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr_1.png</t>
+          <t>plita-filtr-pylniki_1.png</t>
         </is>
       </c>
     </row>
     <row r="92" ht="78" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -8221,19 +7762,19 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
         <v>8500</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>50</v>
@@ -8241,25 +7782,25 @@
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
+          <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki_1.png</t>
+          <t>plita-filtr-pylniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="93" ht="78" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -8274,16 +7815,16 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="I93" s="2" t="n">
         <v>13000</v>
@@ -8294,25 +7835,25 @@
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
+          <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig_1.png</t>
+          <t>plita-filtr-pylniki-sal_1.png</t>
         </is>
       </c>
     </row>
     <row r="94" ht="78" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -8323,23 +7864,23 @@
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>50</v>
@@ -8347,25 +7888,25 @@
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
+          <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal_1.png</t>
+          <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="95" ht="78" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -8376,20 +7917,20 @@
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>8500</v>
+        <v>7500</v>
       </c>
       <c r="I95" s="2" t="n">
         <v>12000</v>
@@ -8400,25 +7941,25 @@
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
+          <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="96" ht="78" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -8429,16 +7970,16 @@
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
@@ -8460,7 +8001,7 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig_1.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8061,7 @@
     <row r="98" ht="78" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -8531,16 +8072,16 @@
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 крышки</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 крышки</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
@@ -8566,14 +8107,14 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki_1.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="99" ht="78" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -8584,16 +8125,16 @@
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
@@ -8619,14 +8160,14 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig_1.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="100" ht="78" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -8637,16 +8178,16 @@
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DQ200 DSG7</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
@@ -8672,14 +8213,14 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig_1.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="101" ht="78" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -8690,16 +8231,16 @@
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="n"/>
       <c r="E101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
@@ -8725,7 +8266,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig_1.png, salnik-shtoka-orig_2.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
@@ -9377,7 +8918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9426,6 +8967,90 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>plita-filtr_1.png</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig_1.png</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki_1.png</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig_1.png</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig_1.png</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig_1.png</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig_2.png</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нераспознанные фото" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Товары" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Нераспознанные фото" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -171,13 +171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -196,13 +196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -221,13 +221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -246,13 +246,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -271,13 +271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -296,13 +296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -321,13 +321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -346,13 +346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -371,13 +371,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -396,13 +396,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -421,13 +421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -446,13 +446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -471,13 +471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -496,13 +496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -521,13 +521,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -546,13 +546,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -571,13 +571,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -596,13 +596,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -621,13 +621,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -646,13 +646,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -671,13 +671,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -696,13 +696,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -721,13 +721,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -746,13 +746,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -771,13 +771,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -796,13 +796,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -821,13 +821,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -846,13 +846,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -871,13 +871,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -896,13 +896,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -921,13 +921,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -946,13 +946,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -971,13 +971,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -996,13 +996,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1021,13 +1021,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1046,13 +1046,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1071,13 +1071,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1096,13 +1096,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1121,13 +1121,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1146,13 +1146,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1171,13 +1171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1196,13 +1196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1221,13 +1221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1246,13 +1246,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1271,13 +1271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1296,13 +1296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1321,13 +1321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1346,13 +1346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1371,13 +1371,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1396,13 +1396,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1421,13 +1421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1446,13 +1446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1471,13 +1471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1496,13 +1496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1521,13 +1521,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1546,13 +1546,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1571,13 +1571,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1596,13 +1596,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1621,13 +1621,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1646,13 +1646,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1671,13 +1671,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1696,13 +1696,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1721,13 +1721,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1746,13 +1746,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1771,13 +1771,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1796,13 +1796,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1821,13 +1821,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1846,13 +1846,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1871,13 +1871,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1896,13 +1896,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1921,13 +1921,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1946,13 +1946,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1971,13 +1971,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1996,13 +1996,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2021,13 +2021,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2046,13 +2046,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2071,13 +2071,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2096,13 +2096,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2121,13 +2121,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2146,13 +2146,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2171,13 +2171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2196,13 +2196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2221,13 +2221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2246,13 +2246,63 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2267,17 +2317,117 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2292,17 +2442,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2317,17 +2467,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2342,17 +2492,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2367,17 +2517,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2392,17 +2542,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2417,17 +2567,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2442,17 +2592,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2467,17 +2617,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2492,17 +2642,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2517,17 +2667,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2542,17 +2692,17 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2567,17 +2717,167 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>113</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId105"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId106"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>116</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId107"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>118</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2874,7 +3174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3134,7 +3434,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
@@ -3158,21 +3458,19 @@
       <c r="I5" s="2" t="n">
         <v>145000</v>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Подтверждено пользователем: это целый мехатроник в сборе с электронной платой (DQ250/DSG6), не отдельная плата. Образец поменяла на 0am325025HX — тоже 'мехатроник с эл. платой в сборе', ближе по смыслу, чем фильтр 02E305051C.</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>02E927770AL_1.png</t>
@@ -3316,7 +3614,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4950</v>
+        <v>9479</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>12000</v>
@@ -3327,7 +3625,7 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325025B.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
@@ -4610,7 +4908,7 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>850</v>
+        <v>979</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>2000</v>
@@ -4621,7 +4919,7 @@
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025P.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
@@ -5198,12 +5496,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: длинный шток 101мм 0AM325091E + втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект длинный шток 101мм 0AM325091E + DSG7 DQ200</t>
+          <t>Ремкомплект Усиленный длинный шток 0AM325091E + DSG7 DQ200</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -5218,7 +5516,7 @@
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025u.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
@@ -5304,12 +5602,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: короткий шток 99мм 0AM325091F + втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 99мм 0AM325091F + DSG7 DQ200</t>
+          <t>Ремкомплект Усиленный короткий шток 0AM325091F + DSG7 DQ200</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -5324,7 +5622,7 @@
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025z.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
@@ -5441,7 +5739,7 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>879</v>
+        <v>979</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>2000</v>
@@ -5452,7 +5750,7 @@
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025С.&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
@@ -5644,12 +5942,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
@@ -5664,7 +5962,7 @@
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -5687,7 +5985,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
@@ -5711,21 +6009,19 @@
       <c r="I52" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J52" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
           <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 длинных штока 101мм 0AM325091E усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091e. Проверить вес/габариты упаковки под комплект (больше, чем у одиночного штока).</t>
-        </is>
-      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
           <t>0am325091e-set_1.png</t>
@@ -5754,12 +6050,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм 0AM325091F</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -5774,7 +6070,7 @@
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
@@ -5793,7 +6089,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
@@ -5817,9 +6113,7 @@
       <c r="I54" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J54" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -5827,11 +6121,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 коротких штока 99мм 0AM325091F усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091f. Проверить вес/габариты упаковки под комплект.</t>
-        </is>
-      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>0am325091f-set_1.png</t>
@@ -5967,7 +6257,7 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>850</v>
+        <v>931</v>
       </c>
       <c r="I57" s="2" t="n">
         <v>0</v>
@@ -5978,7 +6268,7 @@
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -6650,7 +6940,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
@@ -6669,14 +6959,12 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>3990</v>
+        <v>19800</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>25000</v>
+      </c>
+      <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -6684,11 +6972,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>Образец — 0AM325473 (Соленоиды мехатроника DSG7 DQ200 0AM 0CW), по твоему решению: категория/характеристики 'соленоидов' в Ozon, скорее всего, достаточно общие, чтобы не заводить отдельно через кабинет. Категорию/атрибуты после создания стоит один раз проверить в кабинете Ozon — если что-то не подойдёт (например размеры/вес явно другие для 6T30), поправим вручную.</t>
-        </is>
-      </c>
+      <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>6t30_1.png</t>
@@ -7279,7 +7563,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr"/>
@@ -7303,9 +7587,7 @@
       <c r="I83" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="J83" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J83" s="2" t="n"/>
       <c r="K83" s="2" t="n"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -7313,11 +7595,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
-        </is>
-      </c>
+      <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
           <t>filtr-setka-0b5-orig_1.png</t>
@@ -7332,7 +7610,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
@@ -7356,9 +7634,7 @@
       <c r="I84" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J84" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J84" s="2" t="n"/>
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -7366,11 +7642,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
-        </is>
-      </c>
+      <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
           <t>gidroakkumulyator-orig_1.png, gidroakkumulyator-orig_2.png, gidroakkumulyator-orig_3.png</t>
@@ -7438,7 +7710,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr"/>
@@ -7462,9 +7734,7 @@
       <c r="I86" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J86" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J86" s="2" t="n"/>
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -7472,11 +7742,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
-        </is>
-      </c>
+      <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
           <t>klipsy-shtokov-2sht_1.png</t>
@@ -7491,7 +7757,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr"/>
@@ -7515,9 +7781,7 @@
       <c r="I87" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="J87" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J87" s="2" t="n"/>
       <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -7525,11 +7789,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>Найден через next.png/next-2.png ещё раньше. Отдельный корпус фильтра 0BH325159 — сейчас в каталоге есть только 0BH325183B (сам фильтр) и наборы DQ500/DQ500-a/Dq500 (корпус+фильтр вместе). Образец — 0BH325183B.</t>
-        </is>
-      </c>
+      <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
           <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
@@ -7593,7 +7853,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
@@ -7617,9 +7877,7 @@
       <c r="I89" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="J89" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J89" s="2" t="n"/>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -7627,11 +7885,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 2. Комплект 2 шт — в отличие от одиночной планки 0am325477ae (1 шт).</t>
-        </is>
-      </c>
+      <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
           <t>planka-solenoid-2sht_1.png</t>
@@ -7646,7 +7900,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr"/>
@@ -7670,21 +7924,19 @@
       <c r="I90" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="J90" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J90" s="2" t="n"/>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 2. Только пластины на соленоиды, оригинал VW, без сепараторной пластины (в отличие от связки 0am325025j).</t>
-        </is>
-      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
           <t>plastiny-solenoid-orig_1.png</t>
@@ -7694,12 +7946,12 @@
     <row r="91" ht="78" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
@@ -7709,50 +7961,44 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>8500</v>
+        <v>7500</v>
       </c>
       <c r="I91" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J91" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J91" s="2" t="n"/>
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
-        </is>
-      </c>
+      <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki_1.png</t>
+          <t>plita-filtr_1.png</t>
         </is>
       </c>
     </row>
     <row r="92" ht="78" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr"/>
@@ -7762,50 +8008,44 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
         <v>8500</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13000</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J92" s="2" t="n"/>
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
-        </is>
-      </c>
+      <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig_1.png</t>
+          <t>plita-filtr-pylniki_1.png</t>
         </is>
       </c>
     </row>
     <row r="93" ht="78" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr"/>
@@ -7815,523 +8055,467 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="I93" s="2" t="n">
         <v>13000</v>
       </c>
-      <c r="J93" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J93" s="2" t="n"/>
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
-        </is>
-      </c>
+      <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal_1.png</t>
+          <t>plita-filtr-pylniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="94" ht="78" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>13000</v>
+      </c>
+      <c r="J94" s="2" t="n"/>
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
-        </is>
-      </c>
+      <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
+          <t>plita-filtr-pylniki-sal_1.png</t>
         </is>
       </c>
     </row>
     <row r="95" ht="78" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="I95" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="J95" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="J95" s="2" t="n"/>
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
-        </is>
-      </c>
+      <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="96" ht="78" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>9500</v>
+        <v>7500</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13500</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J96" s="2" t="n"/>
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>plita-filtr-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="97" ht="78" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr"/>
       <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Усиленная гидроплита + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>950</v>
+        <v>9500</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>13500</v>
+      </c>
+      <c r="J97" s="2" t="n"/>
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 4 (2 фото — 'подшипник' и 'подшипники', похоже один и тот же товар). Совсем новая категория, аналогов в каталоге нет. Образец взял 0ambset (тоже подшипники) — категория/атрибуты нужно перепроверить вручную в кабинете Ozon.</t>
-        </is>
-      </c>
+      <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6_1.png, podshipnik-vilki-6_2.png</t>
+          <t>plita-pylniki-salniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="98" ht="78" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 крышки</t>
+          <t>Усиленная гидроплита + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>3990</v>
+        <v>9500</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>6500</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>13500</v>
+      </c>
+      <c r="J98" s="2" t="n"/>
       <c r="K98" s="2" t="n"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>Цена — грубая оценка Клода (аналогичного готового комплекта именно с усиленными поршнями в файле раньше не было, ориентировался на цену поршня по отдельности + похожий комплект с сальниками вместо поршней) — проверьте и поправьте сами.</t>
-        </is>
-      </c>
+      <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>plita-pylniki-salniki-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="99" ht="78" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>1850</v>
+        <v>1240</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="J99" s="2" t="n"/>
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 5. Только пыльники (без сальников и крышек), оригинал VAG.</t>
-        </is>
-      </c>
+      <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>podshipnik-vilki-6_1.png, podshipnik-vilki-6_2.png</t>
         </is>
       </c>
     </row>
     <row r="100" ht="78" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DQ200 DSG7</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 крышки</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>2850</v>
+        <v>3990</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>6500</v>
+      </c>
+      <c r="J100" s="2" t="n"/>
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 3. Оригинал VAG версия существующего аналогового ремкомплекта 0am325025G. Уточнить у поставщика реальную оригинальность/цену закупки.</t>
-        </is>
-      </c>
+      <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>porshni-usil-pylniki-kryshki_1.png</t>
         </is>
       </c>
     </row>
     <row r="101" ht="78" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="n"/>
       <c r="E101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 крышки</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>1490</v>
+        <v>3990</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>6500</v>
+      </c>
+      <c r="J101" s="2" t="n"/>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папки 3 и 5 (2 фото). Оригинал VAG версия обычного аналогового сальника 0AM325413A.</t>
-        </is>
-      </c>
+      <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>porshni-usil-pylniki-kryshki-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="102" ht="78" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с 4 шт DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>2490</v>
+        <v>1850</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>4500</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="J102" s="2" t="n"/>
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папки 1 и 3 (2 фото). Премиум-вариант обычного сальника толкателя 0AM325413A — алюминиевый корпус с гальваническим покрытием.</t>
-        </is>
-      </c>
+      <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum_1.png, salnik-tolkatelya-alum_2.png</t>
+          <t>pylniki-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="103" ht="78" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr"/>
@@ -8341,50 +8525,44 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>1690</v>
+        <v>1850</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2800</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="J103" s="2" t="n"/>
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 4. Только сальники штоков (без пыльников/крышек), комплект 2 шт, аналог (не оригинал).</t>
-        </is>
-      </c>
+      <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht_1.png</t>
+          <t>pylniki-shtokov-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="104" ht="78" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr"/>
@@ -8394,156 +8572,138 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DSG7 DQ200</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>1890</v>
+        <v>2850</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="J104" s="2" t="n"/>
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 5. Только сальники (без пыльников и крышек), оригинал VAG.</t>
-        </is>
-      </c>
+      <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig_1.png</t>
+          <t>remkomplekt-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="105" ht="78" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="2" t="n"/>
       <c r="E105" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок DSG7 DQ200 4 шт</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DQ200 DSG7</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>1950</v>
+        <v>2850</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="J105" s="2" t="n"/>
       <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
-        </is>
-      </c>
+      <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht_1.png, salniki-tolkatelya-4sht_2.png</t>
+          <t>remkomplekt-shtokov-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="106" ht="78" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>999</v>
+        <v>1490</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1700</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="J106" s="2" t="n"/>
       <c r="K106" s="2" t="n"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr">
-        <is>
-          <t>Название взято из уже собранной семантики (та же формулировка, что в seo_keywords.xlsx). Образец 0AM325413A — тоже сальник той же линейки, категория/атрибуты должны подойти.</t>
-        </is>
-      </c>
+      <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-l_1.png</t>
+          <t>salnik-shtoka-orig_1.png, salnik-shtoka-orig_2.png</t>
         </is>
       </c>
     </row>
     <row r="107" ht="78" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr"/>
@@ -8553,103 +8713,91 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>999</v>
+        <v>1490</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1700</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="J107" s="2" t="n"/>
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr">
-        <is>
-          <t>Название взято из уже собранной семантики. Образец 0AM325413A — тоже сальник той же линейки.</t>
-        </is>
-      </c>
+      <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-r_1.png</t>
+          <t>salnik-shtoka-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="108" ht="78" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Усиленные алюминиевые сальники толкателя с 4 шт DSG7 DQ200</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>999</v>
+        <v>2490</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1700</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="J108" s="2" t="n"/>
       <c r="K108" s="2" t="n"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>Название взято из уже собранной семантики (сальник входного вала).</t>
-        </is>
-      </c>
+      <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>salnikvhod_1.png</t>
+          <t>salnik-tolkatelya-alum_1.png, salnik-tolkatelya-alum_2.png</t>
         </is>
       </c>
     </row>
     <row r="109" ht="78" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr"/>
@@ -8659,50 +8807,44 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>999</v>
+        <v>1690</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1700</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>2800</v>
+      </c>
+      <c r="J109" s="2" t="n"/>
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr">
-        <is>
-          <t>ЧЕРНОВИК — в собранной семантике есть 'сальник первичного вала' и 'сальник входного вала', но не 'выходного'. Уточни, это точно отдельная деталь (выходной/вторичный вал) или это то же самое, что 'первичный вал' у вас в терминологии?</t>
-        </is>
-      </c>
+      <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>salnikvihod_1.png</t>
+          <t>salniki-shtokov-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="110" ht="78" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr"/>
@@ -8712,103 +8854,91 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1950</v>
+        <v>1890</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="J110" s="2" t="n"/>
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 4. Новая деталь, аналогов в каталоге нет. Образец — плита 0am325066ae, проверить категорию/атрибуты вручную.</t>
-        </is>
-      </c>
+      <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity_1.png</t>
+          <t>salniki-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="111" ht="78" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr"/>
       <c r="D111" s="2" t="n"/>
       <c r="E111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Полный комплект сальников толкателей вилок DSG7 DQ200 4 шт</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>7400</v>
+        <v>1950</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="J111" s="2" t="n"/>
       <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 3. Полный комплект на все 4 позиции мехатроника — в отличие от одиночного толкателя 0am325066AC. Пересчитать вес/габариты.</t>
-        </is>
-      </c>
+      <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4_1.png</t>
+          <t>salniki-tolkatelya-4sht_1.png, salniki-tolkatelya-4sht_2.png</t>
         </is>
       </c>
     </row>
     <row r="112" ht="78" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr"/>
@@ -8818,50 +8948,44 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>усиленные алюминиевые сальники DSG7 DQ200, комплект 4 + 4</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>8900</v>
+        <v>999</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>1700</v>
+      </c>
+      <c r="J112" s="2" t="n"/>
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr">
-        <is>
-          <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
-        </is>
-      </c>
+      <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt_1.png</t>
+          <t>salnikprivod-l_1.png</t>
         </is>
       </c>
     </row>
     <row r="113" ht="78" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Новый (черновик)</t>
+          <t>Действующий</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr"/>
@@ -8871,36 +8995,312 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>4990</v>
+        <v>999</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7000</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>1700</v>
+      </c>
+      <c r="J113" s="2" t="n"/>
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>salnikprivod-r_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="78" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Сальник входного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Сальник входного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="n"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>salnikvhod_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="78" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Сальник выходного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Сальник выходного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="J115" s="2" t="n"/>
+      <c r="K115" s="2" t="n"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>salnikvihod_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="78" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J116" s="2" t="n"/>
+      <c r="K116" s="2" t="n"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="78" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr"/>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>7400</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J117" s="2" t="n"/>
+      <c r="K117" s="2" t="n"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="78" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники DSG7 DQ200, комплект 4 + 4</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>8900</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="2" t="n"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="78" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>4990</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J119" s="2" t="n"/>
+      <c r="K119" s="2" t="n"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr">
-        <is>
-          <t>Архив дизайнера, папка 2. Только втулки (без штоков), комплект 2 шт — в отличие от одиночной втулки 0am325025D.</t>
-        </is>
-      </c>
-      <c r="O113" s="2" t="inlineStr">
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>vtulki-shtokov-2sht_1.png</t>
         </is>
@@ -8918,7 +9318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8967,90 +9367,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>plita-filtr_1.png</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig_1.png</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki_1.png</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig_1.png</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>remkomplekt-shtokov-orig_1.png</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>remkomplekt-shtokov-orig</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig_1.png</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig_2.png</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Товары" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Нераспознанные фото" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нераспознанные фото" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -171,13 +171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -196,13 +196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -221,13 +221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -246,13 +246,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -271,13 +271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -296,13 +296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -321,13 +321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -346,13 +346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -371,13 +371,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -396,13 +396,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -421,13 +421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -446,13 +446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -471,13 +471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -496,13 +496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -521,13 +521,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -546,13 +546,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -571,13 +571,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -596,13 +596,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -621,13 +621,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -646,13 +646,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -671,13 +671,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -696,13 +696,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -721,13 +721,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -746,13 +746,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -771,13 +771,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -796,13 +796,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -821,13 +821,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -846,13 +846,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -871,13 +871,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -896,13 +896,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -921,13 +921,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -946,13 +946,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -971,13 +971,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -996,13 +996,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1021,13 +1021,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1046,13 +1046,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1071,13 +1071,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1096,13 +1096,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1121,13 +1121,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1146,13 +1146,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1171,13 +1171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1196,13 +1196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1221,13 +1221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1246,13 +1246,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1271,13 +1271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId45"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1296,13 +1296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId46"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1321,13 +1321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId47"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1346,13 +1346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId48"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1371,13 +1371,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1396,13 +1396,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1421,13 +1421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId51"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1446,13 +1446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId52"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1471,13 +1471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId53"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1496,13 +1496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId54"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1521,13 +1521,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId55"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1546,13 +1546,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId56"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1571,13 +1571,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId57"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1596,13 +1596,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId58"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1621,13 +1621,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId59"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1646,13 +1646,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1671,13 +1671,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1696,13 +1696,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId62"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1721,13 +1721,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1746,13 +1746,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1771,13 +1771,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1796,13 +1796,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1821,13 +1821,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1846,13 +1846,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1871,13 +1871,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1896,13 +1896,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId70"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1921,13 +1921,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId71"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1946,13 +1946,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId72"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1971,13 +1971,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId73"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1996,13 +1996,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId74"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2021,13 +2021,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId75"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2046,13 +2046,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId76"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2071,13 +2071,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2096,13 +2096,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2121,13 +2121,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId79"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2146,13 +2146,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId80"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2171,13 +2171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId81"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2196,13 +2196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId82"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2221,13 +2221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2246,13 +2246,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2271,13 +2271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2296,13 +2296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2321,13 +2321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2346,13 +2346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2371,13 +2371,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2396,13 +2396,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId90"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2421,13 +2421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId91"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2446,13 +2446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId92"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2471,13 +2471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId93"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2496,13 +2496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId94"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2521,13 +2521,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2546,13 +2546,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId96"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2571,13 +2571,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2596,13 +2596,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2621,13 +2621,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2646,13 +2646,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2671,13 +2671,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId101"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2696,13 +2696,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2721,13 +2721,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2746,13 +2746,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2771,13 +2771,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId105"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2796,13 +2796,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId106"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2821,13 +2821,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId107"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2846,13 +2846,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2871,13 +2871,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId109"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -3422,7 +3422,7 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>02E305051C_1.jpg, 02E305051C_1.png</t>
+          <t>02E305051C_1.png, 02E305051C_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0AM325473_1.jpg, 0AM325473_1.png</t>
+          <t>0AM325473_1.png, 0AM325473_1.jpg</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0am325025H-1.png, 0am325025H_1.jpg</t>
+          <t>0am325025H_1.jpg, 0am325025H-1.png</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0am325025n_1.jpg, 0am325025n_1.png</t>
+          <t>0am325025n_1.png, 0am325025n_1.jpg</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad_1.jpg, 0am325066ad_1.png</t>
+          <t>0am325066ad_1.png, 0am325066ad_1.jpg</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025-2.png, 0cw0am325025.png, 0cw0am325025_1.png</t>
+          <t>0cw0am325025.png, 0cw0am325025_1.png, 0cw0am325025-2.png</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>DQ500-a-1.png, DQ500_1.png, DQ500_3.png, DQ500_a-2.png, dq500.png</t>
+          <t>DQ500-a-1.png, DQ500_a-2.png, DQ500_1.png, DQ500_3.png</t>
         </is>
       </c>
     </row>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -886,7 +886,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -911,7 +911,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -936,7 +936,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -961,7 +961,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -986,7 +986,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1011,7 +1011,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1036,7 +1036,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1061,7 +1061,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1086,7 +1086,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1111,7 +1111,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1136,7 +1136,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1161,7 +1161,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1186,7 +1186,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1211,7 +1211,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1236,7 +1236,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1261,7 +1261,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1286,7 +1286,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1311,7 +1311,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1336,7 +1336,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1361,7 +1361,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1386,7 +1386,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1411,7 +1411,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1436,7 +1436,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1461,7 +1461,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1486,7 +1486,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1511,7 +1511,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1536,7 +1536,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1561,7 +1561,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1586,7 +1586,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1611,7 +1611,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1636,7 +1636,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1661,7 +1661,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1686,7 +1686,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1711,7 +1711,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1736,7 +1736,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1761,7 +1761,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1786,7 +1786,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1811,7 +1811,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1836,7 +1836,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1861,7 +1861,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1886,7 +1886,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1911,7 +1911,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1936,7 +1936,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1961,7 +1961,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1986,7 +1986,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2011,7 +2011,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2036,7 +2036,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2061,7 +2061,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2086,7 +2086,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2111,7 +2111,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2136,7 +2136,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2161,7 +2161,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2186,7 +2186,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2211,7 +2211,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2236,7 +2236,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2261,7 +2261,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2286,7 +2286,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2311,7 +2311,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2336,7 +2336,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2361,7 +2361,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2386,7 +2386,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2411,7 +2411,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2436,7 +2436,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2461,7 +2461,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2486,7 +2486,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2511,7 +2511,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2536,7 +2536,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2561,7 +2561,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2586,7 +2586,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>107</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2611,7 +2611,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>108</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2636,7 +2636,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2661,7 +2661,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2686,7 +2686,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2711,7 +2711,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2736,7 +2736,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2761,7 +2761,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2786,7 +2786,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2811,7 +2811,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>116</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2836,7 +2836,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2847,31 +2847,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="109" name="Image 109" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3601,7 +3576,7 @@
       </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -3632,7 +3607,7 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0AM325025B_1.png, 0AM325025B_2.png, 0AM325025B_3.png</t>
+          <t>0AM325025B_1.png, 0AM325025B_2.png</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3736,7 @@
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -3792,7 +3767,7 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0AM325219C_1.png, 0AM325219C_2.png</t>
+          <t>0AM325219C_1.png</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3842,7 @@
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -3898,7 +3873,7 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0AM325433E_1.png, 0AM325433E_2.png</t>
+          <t>0AM325433E_1.png</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3895,7 @@
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -3955,7 +3930,7 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0AM325443D_1.png, 0AM325443D_2.png, 0AM325443D_3.png</t>
+          <t>0AM325443D_1.png, 0AM325443D_2.png</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3952,7 @@
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -4008,7 +3983,7 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0AM325467J_1.png, 0AM325467J_2.png</t>
+          <t>0AM325467J_2.png</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4058,7 @@
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -4114,7 +4089,7 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0AM325587E_1.png, 0AM325587E_2.png, 0AM325587E_3.png, 0AM325587E_4.png</t>
+          <t>0AM325587E_1.png, 0AM325587E_2.png, 0AM325587E_3.png</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4164,7 @@
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -4220,7 +4195,7 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0AM927769N_1.png, 0AM927769N_2.png</t>
+          <t>0AM927769N_1.png</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4543,7 @@
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -4599,7 +4574,7 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0am325025.png, 0am325025_1.png</t>
+          <t>0am325025.png</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4596,7 @@
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -4652,7 +4627,7 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0am325025D_1.png, 0am325025D_2.png</t>
+          <t>0am325025D_1.png</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4698,7 @@
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -4758,7 +4733,7 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0am325025H_1.jpg, 0am325025H-1.png</t>
+          <t>0am325025H-1.png, 0am325025H_2.png, 0am325025H_3.png, 0am325025H_4.jpg</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4813,7 @@
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -4873,7 +4848,7 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0am325025HX_1.png, 0am325025HX_2.png</t>
+          <t>0am325025HX_1.png, 0am325025HX_2.png, 0am325025HX_3.png</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4870,7 @@
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -4926,7 +4901,7 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0am325025P_1.png, 0am325025P_2.png</t>
+          <t>0am325025P_1.png</t>
         </is>
       </c>
     </row>
@@ -5007,7 +4982,7 @@
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -5042,7 +5017,7 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0am325025ae_1.png, 0am325025ae_2.png</t>
+          <t>0am325025ae_2.png</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5092,7 @@
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -5148,7 +5123,7 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0am325025h.png, 0am325025h_1.png, 0am325025h_3.png, 0am325025h_4.png, 0am325025h_6.png</t>
+          <t>фото уже на карточке Ozon, локального файла нет: https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h.png</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5145,7 @@
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -5205,7 +5180,7 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0am325025j_1.png, 0am325025j_2.png</t>
+          <t>0am325025j_1.png</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5202,7 @@
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -5258,7 +5233,7 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0am325025l.png, 0am325025l_1.png</t>
+          <t>0am325025l.png</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5286,7 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0am325025m_1.png</t>
+          <t>0am325025m.png</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5308,7 @@
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -5364,7 +5339,7 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0am325025n_1.png, 0am325025n_1.jpg</t>
+          <t>0am325025n_1.jpg</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5361,7 @@
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -5417,7 +5392,7 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0am325025q_1.png, 0am325025q_2.png</t>
+          <t>0am325025q_1.png</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5913,7 @@
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -5973,7 +5948,7 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0am325091e.png, 0am325091e_1.png</t>
+          <t>0am325091e.png</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6021,7 @@
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -6077,7 +6052,7 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0am325091f.png, 0am325091f_1.png</t>
+          <t>0am325091f.png</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6121,7 @@
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -6177,7 +6152,7 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae_1.png, 0am325477ae_2.png, 0am325477ae_3.png, 0am325477ae_4.png</t>
+          <t>0am325477ae_1.png</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6378,7 @@
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -6438,7 +6413,7 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0cw325025h_1.png, 0cw325025h_2.png, 0cw325025h_3.png, 0cw325025h_4.png</t>
+          <t>0cw325025h_1.png</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7591,7 @@
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -7645,7 +7620,7 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig_1.png, gidroakkumulyator-orig_2.png, gidroakkumulyator-orig_3.png</t>
+          <t>gidroakkumulyator-orig_3.png</t>
         </is>
       </c>
     </row>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -211,7 +211,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -236,7 +236,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -261,7 +261,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -286,7 +286,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -311,7 +311,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -336,7 +336,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -361,7 +361,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -386,7 +386,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -411,7 +411,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -436,7 +436,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -461,7 +461,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -486,7 +486,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -511,7 +511,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -536,7 +536,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -561,7 +561,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -586,7 +586,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -611,7 +611,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -636,7 +636,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -661,7 +661,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -686,7 +686,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -711,7 +711,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -736,7 +736,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -761,7 +761,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -786,7 +786,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -811,7 +811,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -836,7 +836,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -861,7 +861,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -886,7 +886,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -911,7 +911,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -936,7 +936,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -961,7 +961,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -986,7 +986,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1011,7 +1011,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1036,7 +1036,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1061,7 +1061,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1086,7 +1086,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1111,7 +1111,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1136,7 +1136,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1161,7 +1161,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1186,7 +1186,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1211,7 +1211,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1236,7 +1236,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1261,7 +1261,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1286,7 +1286,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1311,7 +1311,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1336,7 +1336,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1361,7 +1361,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1386,7 +1386,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1411,7 +1411,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1436,7 +1436,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1461,7 +1461,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1486,7 +1486,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1511,7 +1511,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1536,7 +1536,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1561,7 +1561,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1586,7 +1586,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1611,7 +1611,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1636,7 +1636,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1661,7 +1661,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1686,7 +1686,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1711,7 +1711,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1736,7 +1736,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1761,7 +1761,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1786,7 +1786,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1811,7 +1811,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1836,7 +1836,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1861,7 +1861,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1886,7 +1886,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1911,7 +1911,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1936,7 +1936,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1961,7 +1961,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1986,7 +1986,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2011,7 +2011,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2036,7 +2036,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2061,7 +2061,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2086,7 +2086,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2111,7 +2111,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2136,7 +2136,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2161,7 +2161,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2186,7 +2186,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2211,7 +2211,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2236,7 +2236,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2261,7 +2261,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2286,7 +2286,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2311,7 +2311,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2336,7 +2336,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2361,7 +2361,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2386,7 +2386,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2411,7 +2411,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2436,7 +2436,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2461,7 +2461,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2486,7 +2486,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2511,7 +2511,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2536,7 +2536,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2561,7 +2561,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>107</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2586,7 +2586,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>108</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2611,7 +2611,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2636,7 +2636,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2661,7 +2661,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2686,7 +2686,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2711,7 +2711,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2736,7 +2736,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2761,7 +2761,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2786,7 +2786,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>116</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2811,7 +2811,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -2836,7 +2836,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>118</row>
+      <row>119</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -3149,7 +3149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O119"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Цена WB, ₽ (только для новых WB-товаров)</t>
+          <t>Цена WB, ₽ (финальная, покупателю)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -3285,7 +3285,9 @@
       <c r="J2" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="K2" s="2" t="n"/>
+      <c r="K2" s="2" t="n">
+        <v>675</v>
+      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
@@ -3351,14 +3353,10 @@
     <row r="4" ht="78" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>02E305051C</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>02E305045E</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -3366,45 +3364,37 @@
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1879</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="K4" s="2" t="n"/>
+          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n">
+        <v>1800</v>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+          <t>Корпус фильтра DQ250 DSG6 02E305045 Новый улучшает теплоотвод отличное качество - проверенный!</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>02E305051C_1.png, 02E305051C_1.jpg</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3412,50 +3402,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG6 DQ250 в сборе с электронной 02E927770AL</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>118000</v>
+        <v>1879</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>145000</v>
-      </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
+        <v>3000</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1770</v>
+      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
-        </is>
-      </c>
+          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>02E927770AL_1.png</t>
+          <t>02E305051C_1.png, 02E305051C_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3463,52 +3457,50 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной 02E927770AL</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3879</v>
+        <v>118000</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>87</v>
-      </c>
+        <v>145000</v>
+      </c>
+      <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>02e305045_1.png, 02e305045_2.png, 02e305045_3.png, 02e305045_4.png</t>
+          <t>02E927770AL_1.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3523,45 +3515,47 @@
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1479</v>
+        <v>3879</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="K7" s="2" t="n"/>
+        <v>87</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
+          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0AM301212A_1.jpg, 0AM301212A_1.png</t>
+          <t>02e305045_1.png, 02e305045_2.png, 02e305045_3.png, 02e305045_4.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3580,44 +3574,50 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9479</v>
+        <v>1479</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>975</v>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0AM325025B_1.png, 0AM325025B_2.png</t>
+          <t>0AM301212A_1.jpg, 0AM301212A_1.png</t>
         </is>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>0AM325091E / 0AM325091F</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
+          <t>0AM325025B</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -3625,19 +3625,72 @@
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>9479</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>8244.5</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0AM325025B_1.png, 0AM325025B_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>0AM325091E / 0AM325091F</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Сальник штока DSG7 DQ200 0AM 0CW оригинал Volkswagen</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n">
+        <v>1319.7</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -3657,71 +3710,18 @@
 Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>0AM325120A</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>999</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0AM325120A_1.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -3740,41 +3740,43 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>3479</v>
+        <v>999</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="K11" s="2" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>675</v>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0AM325219C_1.png</t>
+          <t>0AM325120A_1.png</t>
         </is>
       </c>
     </row>
     <row r="12" ht="78" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3793,41 +3795,43 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>999</v>
+        <v>3479</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="K12" s="2" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>2475</v>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
+          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A_1.png</t>
+          <t>0AM325219C_1.png</t>
         </is>
       </c>
     </row>
     <row r="13" ht="78" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -3846,41 +3850,43 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1479</v>
+        <v>999</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="K13" s="2" t="n"/>
+        <v>83</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>675</v>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0AM325433E_1.png</t>
+          <t>0AM325413A_1.png</t>
         </is>
       </c>
     </row>
     <row r="14" ht="78" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3895,49 +3901,47 @@
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1990</v>
+        <v>1479</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="K14" s="2" t="n"/>
+        <v>87</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1250</v>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #dsg_ремонт #dsg_обслуживание #dq2000amdsg</t>
-        </is>
-      </c>
+          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0AM325443D_1.png, 0AM325443D_2.png</t>
+          <t>0AM325433E_1.png</t>
         </is>
       </c>
     </row>
     <row r="15" ht="78" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3952,45 +3956,51 @@
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина VAG DSG7 DQ200 0AM325467J</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
         <v>1990</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K15" s="2" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>1470</v>
+      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #dsg_ремонт #dsg_обслуживание #dq2000amdsg</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0AM325467J_2.png</t>
+          <t>0AM325443D_1.png, 0AM325443D_2.png</t>
         </is>
       </c>
     </row>
     <row r="16" ht="78" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -4005,45 +4015,47 @@
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
+          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
+          <t>Оригинальная сепараторная пластина VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>11979</v>
+        <v>1990</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1400</v>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0AM325473_1.png, 0AM325473_1.jpg</t>
+          <t>0AM325467J_2.png</t>
         </is>
       </c>
     </row>
     <row r="17" ht="78" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -4058,45 +4070,47 @@
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>8890</v>
+        <v>11979</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K17" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>8784.299999999999</v>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0AM325587E_1.png, 0AM325587E_2.png, 0AM325587E_3.png</t>
+          <t>0AM325473_1.png, 0AM325473_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="18" ht="78" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -4111,49 +4125,47 @@
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>78800</v>
+        <v>8890</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>80000</v>
+        <v>12000</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="2" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>9743.5</v>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg7 #dsg7_dq200 #dsg7_mechatronic #электроннаяплатаdq200</t>
-        </is>
-      </c>
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0AM927769D_1.png</t>
+          <t>0AM325587E_1.png, 0AM325587E_2.png, 0AM325587E_3.png</t>
         </is>
       </c>
     </row>
     <row r="19" ht="78" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -4161,48 +4173,58 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Прокладки электронной платы DSG7 DQ200 0AM927769N</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>3479</v>
+        <v>78800</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4500</v>
+        <v>80000</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="K19" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>2475</v>
+      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg7 #dsg7_dq200 #dsg7_mechatronic #электроннаяплатаdq200</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0AM927769N_1.png</t>
+          <t>0AM927769D_1.png</t>
         </is>
       </c>
     </row>
     <row r="20" ht="78" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -4213,49 +4235,45 @@
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Прокладки электронной платы DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3879</v>
+        <v>3479</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
-        </is>
-      </c>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0BH325_1.jpg, 0BH325_1.png, 0BH325_2.png, 0BH325_3.png</t>
+          <t>0AM927769N_1.png</t>
         </is>
       </c>
     </row>
     <row r="21" ht="78" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -4263,14 +4281,10 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -4283,32 +4297,36 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>7979</v>
+        <v>3879</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0BH325183_1.png, 0BH325183_2.png</t>
+          <t>0BH325_1.jpg, 0BH325_1.png, 0BH325_2.png, 0BH325_3.png</t>
         </is>
       </c>
     </row>
     <row r="22" ht="78" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -4327,12 +4345,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -4342,29 +4360,35 @@
         <v>10000</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0BH325183 B_1.png, 0BH325183 B_2.png</t>
+          <t>0BH325183_1.png, 0BH325183_2.png</t>
         </is>
       </c>
     </row>
     <row r="23" ht="78" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr"/>
+          <t>0BH325183 B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -4372,19 +4396,72 @@
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>7979</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0BH325183 B_1.png, 0BH325183 B_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="78" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Алюминиевый корпус фильтра DSG7 DQ500 — 0BH325183B
 Надёжный алюминиевый корпус фильтра, совместимый с 7-ступенчатой коробкой передач DSG DQ500 с мокрым сцеплением. Является лучшей альтернативой пластиковому варианту — отлично справляется с охлаждением и защитой масляного фильтра.
@@ -4404,41 +4481,43 @@
 Резиновое кольцо в комплекте</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0BH325183B_1.png, 0BH325183B_2.png, 0BH325183B_3.png</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="78" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>0BH325183BB</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n">
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n">
+        <v>2732.24</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -4460,41 +4539,43 @@
 </t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="78" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26" ht="78" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>0am3250066AE</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n">
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроник DQ200 DSG7+оригинал пыльник сальник W</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n">
+        <v>15032.1</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW ОРИГИНАЛЫ РАСХОДНИКИ Volkswagen
 В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.
@@ -4517,71 +4598,18 @@
 </t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="78" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 гидроплита 0AM325025</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>12890</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>18000</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
-        </is>
-      </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0am325025.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="78" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -4600,41 +4628,43 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 гидроплита 0AM325025</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>2890</v>
+        <v>12890</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="K27" s="2" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>10800</v>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0am325025D_1.png</t>
+          <t>0am325025.png</t>
         </is>
       </c>
     </row>
     <row r="28" ht="78" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -4649,45 +4679,47 @@
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200 пыльники крышки</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>3879</v>
+        <v>2890</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="K28" s="2" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>2650</v>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0am325025G_1.png, 0am325025G_2.png, 0am325025G_3.png</t>
+          <t>0am325025D_1.png</t>
         </is>
       </c>
     </row>
     <row r="29" ht="78" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -4695,75 +4727,132 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200 пыльники крышки</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>68800</v>
+        <v>3879</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>90000</v>
+        <v>6000</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K29" s="2" t="n"/>
+        <v>93</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>3760</v>
+      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #мехатроник_dq200 #dsg7 #dsg7_dq200 #dsg7_0am_dq200 #0am325066ae #0am325066ac #0am325066 #dq200ремкомплект #0am325025 #0am325025d</t>
-        </is>
-      </c>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0am325025H-1.png, 0am325025H_2.png, 0am325025H_3.png, 0am325025H_4.jpg</t>
+          <t>0am325025G_1.png, 0am325025G_2.png, 0am325025G_3.png</t>
         </is>
       </c>
     </row>
     <row r="30" ht="78" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>0am325025HC</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>0am325025H</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроник DSG7 DQ200+пыльник сальник Оригинал</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
+          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>68800</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>90000</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #мехатроник_dq200 #dsg7 #dsg7_dq200 #dsg7_0am_dq200 #0am325066ae #0am325066ac #0am325066 #dq200ремкомплект #0am325025 #0am325025d</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0am325025H-1.png, 0am325025H_2.png, 0am325025H_3.png, 0am325025H_4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="78" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>0am325025HC</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроник DSG7 DQ200+пыльник сальник Оригинал</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n">
+        <v>9743.5</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)
 Описание товара
@@ -4787,75 +4876,18 @@
 </t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="78" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>0am325025HX</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG7 DQ200 в сборе с электронной 0AM927769D</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>128800</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0am325025HX_1.png, 0am325025HX_2.png, 0am325025HX_3.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="78" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4870,48 +4902,58 @@
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной 0AM927769D</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>979</v>
+        <v>128800</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2000</v>
+        <v>150000</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="K32" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>113525</v>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0am325025P_1.png</t>
+          <t>0am325025HX_1.png, 0am325025HX_2.png, 0am325025HX_3.png</t>
         </is>
       </c>
     </row>
     <row r="33" ht="78" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
+          <t>0am325025P</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -4919,19 +4961,72 @@
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0am325025P_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="78" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>0am325025Y</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n">
+        <v>85025</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников (как на фото) Максимально профессиональное восстановление в заводских условиях + проверка на стенде = отличный результат и гарантия работоспособности.
 без электронной платы только гидравлика
@@ -4956,75 +5051,18 @@
 </t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="78" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>0am325025ae</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>усиленная прокладка мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>4879</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0am325025ae_2.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="78" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -5043,41 +5081,47 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
+          <t>усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>3879</v>
+        <v>4879</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="K35" s="2" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>3920</v>
+      </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0am325025f_1.png</t>
+          <t>0am325025ae_2.png</t>
         </is>
       </c>
     </row>
     <row r="36" ht="78" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>0am325025h</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5092,45 +5136,47 @@
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1990</v>
+        <v>3879</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="K36" s="2" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>4440</v>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h.png</t>
+          <t>0am325025f_1.png</t>
         </is>
       </c>
     </row>
     <row r="37" ht="78" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025h</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -5145,49 +5191,47 @@
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2879</v>
+        <v>1990</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="K37" s="2" t="n"/>
+        <v>93</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>4160</v>
+      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
-        </is>
-      </c>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0am325025j_1.png</t>
+          <t>фото уже на карточке Ozon, локального файла нет: https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h.png</t>
         </is>
       </c>
     </row>
     <row r="38" ht="78" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5206,41 +5250,47 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1490</v>
+        <v>2879</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2300</v>
+        <v>5000</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="K38" s="2" t="n"/>
+        <v>88</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1950</v>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0am325025l.png</t>
+          <t>0am325025j_1.png</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -5259,41 +5309,43 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>8879</v>
+        <v>1490</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>12000</v>
+        <v>2300</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="K39" s="2" t="n"/>
+        <v>86</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1325</v>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
+          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0am325025m.png</t>
+          <t>0am325025l.png</t>
         </is>
       </c>
     </row>
     <row r="40" ht="78" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -5312,41 +5364,43 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8979</v>
+        <v>8879</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>12000</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K40" s="2" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>8443.5</v>
+      </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0am325025n_1.jpg</t>
+          <t>0am325025m.png</t>
         </is>
       </c>
     </row>
     <row r="41" ht="78" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -5365,41 +5419,43 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>979</v>
+        <v>8979</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1800</v>
+        <v>12000</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="K41" s="2" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>8378.5</v>
+      </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0am325025q_1.png</t>
+          <t>0am325025n_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="42" ht="78" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -5418,41 +5474,43 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1479</v>
+        <v>979</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="K42" s="2" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>980</v>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0am325025r_1.png</t>
+          <t>0am325025q_1.png</t>
         </is>
       </c>
     </row>
     <row r="43" ht="78" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -5471,41 +5529,43 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный длинный шток 0AM325091E + DSG7 DQ200</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>4490</v>
+        <v>1479</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K43" s="2" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1475</v>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0am325025u_1.png</t>
+          <t>0am325025r_1.png</t>
         </is>
       </c>
     </row>
     <row r="44" ht="78" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -5513,52 +5573,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+          <t>Ремкомплект Усиленный длинный шток 0AM325091E + DSG7 DQ200</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>78475</v>
+        <v>4490</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>90000</v>
+        <v>6000</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="2" t="n"/>
+        <v>82</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>3430</v>
+      </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
-        </is>
-      </c>
+          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0am325025x_1.jpg</t>
+          <t>0am325025u_1.png</t>
         </is>
       </c>
     </row>
     <row r="45" ht="78" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -5566,55 +5628,59 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный короткий шток 0AM325091F + DSG7 DQ200</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>4490</v>
+        <v>78475</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>6000</v>
+        <v>90000</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0am325025z.png</t>
+          <t>0am325025x_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="46" ht="78" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>0am325025ze</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr"/>
+          <t>0am325025z</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -5622,19 +5688,72 @@
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект Усиленный короткий шток 0AM325091F + DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>4490</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>3430</v>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0am325025z.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="78" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>0am325025ze</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DQ200 DSG7 0AM Новые соленоиды Bosch</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n">
+        <v>69302.22</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Абсолютно новый мехатроник DSG7 DQ200 (0AM / 0CW) — гидравлическая часть
 В продаже полностью восстановленный до состояния нового мехатроник DSG7 DQ200 для коробок передач 0AM и 0CW. Узел собран с использованием новых оригинальных и OEM-компонентов, прошёл обязательную проверку и готов к установке.
@@ -5675,71 +5794,18 @@
 Капитальном ремонте коробки DQ200</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="78" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>0am325025С</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
-        </is>
-      </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0am325025С_1.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="78" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -5758,41 +5824,43 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1479</v>
+        <v>979</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K48" s="2" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>980</v>
+      </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0am325066AC_1.png</t>
+          <t>0am325025С_1.png</t>
         </is>
       </c>
     </row>
     <row r="49" ht="78" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -5807,45 +5875,47 @@
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>979</v>
+        <v>1479</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K49" s="2" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1325</v>
+      </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad_1.png, 0am325066ad_1.jpg</t>
+          <t>0am325066AC_1.png</t>
         </is>
       </c>
     </row>
     <row r="50" ht="78" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -5864,41 +5934,43 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>8879</v>
+        <v>979</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="K50" s="2" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>980</v>
+      </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae_1.png, 0am325066ae_4.png</t>
+          <t>0am325066ad_1.png, 0am325066ad_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="51" ht="78" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -5913,49 +5985,47 @@
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>2879</v>
+        <v>8879</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="K51" s="2" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>7347.3</v>
+      </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dsg7</t>
-        </is>
-      </c>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0am325091e.png</t>
+          <t>0am325066ae_1.png, 0am325066ae_4.png</t>
         </is>
       </c>
     </row>
     <row r="52" ht="78" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -5963,32 +6033,40 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>8850</v>
+        <v>2879</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
+        <v>5000</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>2850</v>
+      </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
+          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -5999,14 +6077,14 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0am325091e-set_1.png</t>
+          <t>0am325091e.png</t>
         </is>
       </c>
     </row>
     <row r="53" ht="78" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -6014,52 +6092,50 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм 0AM325091F</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 DSG7 DQ200</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2879</v>
+        <v>8850</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>29</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0am325091f.png</t>
+          <t>0am325091e-set_1.png</t>
         </is>
       </c>
     </row>
     <row r="54" ht="78" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6067,46 +6143,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм 0AM325091F</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>8850</v>
+        <v>2879</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
+        <v>5000</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>2950</v>
+      </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0am325091f-set_1.png</t>
+          <t>0am325091f.png</t>
         </is>
       </c>
     </row>
     <row r="55" ht="78" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6114,52 +6198,46 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 DSG7 DQ200</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>2479</v>
+        <v>8850</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>12</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae_1.png</t>
+          <t>0am325091f-set_1.png</t>
         </is>
       </c>
     </row>
     <row r="56" ht="78" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6167,48 +6245,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200 10 шт оригинал</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>11979</v>
+        <v>2479</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>2447.15</v>
+      </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0ambset_1.png, 0ambset_2.png</t>
+          <t>0am325477ae_1.png</t>
         </is>
       </c>
     </row>
     <row r="57" ht="78" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6223,45 +6307,41 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200 10 шт оригинал</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>931</v>
+        <v>11979</v>
       </c>
       <c r="I57" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J57" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>49</v>
       </c>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdsg7dq200</t>
-        </is>
-      </c>
+          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0cw0am_1.jpg, 0cw0am_1.png</t>
+          <t>0ambset_1.png, 0ambset_2.png</t>
         </is>
       </c>
     </row>
     <row r="58" ht="78" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6272,49 +6352,49 @@
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>16890</v>
+        <v>931</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкиdq200</t>
+          <t>#Прокладкаdsg7dq200</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025.png, 0cw0am325025_1.png, 0cw0am325025-2.png</t>
+          <t>0cw0am_1.jpg, 0cw0am_1.png</t>
         </is>
       </c>
     </row>
     <row r="59" ht="78" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -6325,49 +6405,49 @@
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>850</v>
+        <v>16890</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1500</v>
+        <v>25000</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкаdq200dsg</t>
+          <t>#Прокладкиdq200</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200_1.jpg</t>
+          <t>0cw0am325025.png, 0cw0am325025_1.png, 0cw0am325025-2.png</t>
         </is>
       </c>
     </row>
     <row r="60" ht="78" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6382,45 +6462,45 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы DSG7 DQ200 0AM927769N</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1290</v>
+        <v>850</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+          <t>#Прокладкаdq200dsg</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0cw325025h_1.png</t>
+          <t>0cw0amdsgdq200_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="61" ht="78" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -6431,45 +6511,49 @@
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Прокладка электронной платы DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1490</v>
+        <v>1290</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0сц_1.png, 0сц_2.png, 0сц_3.png, 0сц_4.png, 0сц_5.png, 0сц_6.png, 0сц_7.png</t>
+          <t>0cw325025h_1.png</t>
         </is>
       </c>
     </row>
     <row r="62" ht="78" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -6477,52 +6561,48 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>979</v>
+        <v>1490</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>122390AK-AF_1.jpg, 122390AK-AF_1.png</t>
+          <t>0сц_1.png, 0сц_2.png, 0сц_3.png, 0сц_4.png, 0сц_5.png, 0сц_6.png, 0сц_7.png</t>
         </is>
       </c>
     </row>
     <row r="63" ht="78" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -6537,45 +6617,47 @@
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1490</v>
+        <v>979</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="K63" s="2" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>980</v>
+      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>122390AKAF_1.png</t>
+          <t>122390AK-AF_1.jpg, 122390AK-AF_1.png</t>
         </is>
       </c>
     </row>
     <row r="64" ht="78" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -6590,45 +6672,47 @@
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1479</v>
+        <v>1490</v>
       </c>
       <c r="I64" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K64" s="2" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>1319.7</v>
+      </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>123014‑AF_1.png, 123014‑AF_2.png</t>
+          <t>122390AKAF_1.png</t>
         </is>
       </c>
     </row>
     <row r="65" ht="78" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -6643,52 +6727,54 @@
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>58900</v>
+        <v>1479</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>80000</v>
+        <v>2500</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="2" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>1225</v>
+      </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>#гидроблокjf011e</t>
-        </is>
-      </c>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>31705-1XF0C_1.jpg</t>
+          <t>123014‑AF_1.png, 123014‑AF_2.png</t>
         </is>
       </c>
     </row>
     <row r="66" ht="78" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr"/>
+          <t>31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -6696,19 +6782,76 @@
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>58900</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="n">
+        <v>40052</v>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf011e</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>31705-1XF0C_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="78" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>31705-1XF1A</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E Старое поколение Nissan Mitsubishi Renault</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n">
+        <v>40052</v>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E Старое поколение для вариатора CVT RE0F10A. Восстанавливает давление масла и стабильную работу трансмиссии. Прямая замена штатного узла без доработок.
 Гидроблок вариатора JF011E Старое поколение — управляющий узел CVT-коробки, отвечающий за распределение давления масла и работу соленоидов. Применяется в вариаторах RE0F10A и устанавливается на автомобили Nissan, Mitsubishi, Renault и Jeep.
@@ -6736,75 +6879,18 @@
 гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi ремонт вариатора jf011e</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="78" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>58900</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>80000</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
-        </is>
-      </c>
+      <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>31705-X428B_1.png, 31705-X428B_2.png, 31705-X428B_3.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="68" ht="78" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -6819,16 +6905,16 @@
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
@@ -6838,26 +6924,32 @@
         <v>80000</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K68" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>42408</v>
+      </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>317053TX0C_1.png</t>
+          <t>31705-X428B_1.png, 31705-X428B_2.png, 31705-X428B_3.png</t>
         </is>
       </c>
     </row>
     <row r="69" ht="78" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -6876,41 +6968,43 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>999</v>
+        <v>58900</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2000</v>
+        <v>80000</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="K69" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>40052</v>
+      </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>55565480_1.png</t>
+          <t>317053TX0C_1.png</t>
         </is>
       </c>
     </row>
     <row r="70" ht="78" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -6918,86 +7012,101 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>19800</v>
+        <v>999</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="n"/>
+        <v>2000</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>980</v>
+      </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>6t30_1.png</t>
+          <t>55565480_1.png</t>
         </is>
       </c>
     </row>
     <row r="71" ht="78" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>DF-DQ250-ALU-KIT</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr"/>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>6t30</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045+масляный фильтр DSG6</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="n"/>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>19800</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>25000</v>
+      </c>
       <c r="J71" s="2" t="n"/>
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
-Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>6t30_1.png</t>
         </is>
       </c>
     </row>
     <row r="72" ht="78" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>DF-DQ500-FH-KIT</t>
+          <t>DF-DQ250-ALU-KIT</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
@@ -7013,14 +7122,58 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + масляный фильтр DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра DSG6 DQ250 02E305045+масляный фильтр DSG6</t>
         </is>
       </c>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
       <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="n"/>
+      <c r="K72" s="2" t="n">
+        <v>2150</v>
+      </c>
       <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
+Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>(нет фото ни локально, ни на карточке)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="78" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>DF-DQ500-FH-KIT</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + масляный фильтр DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n">
+        <v>1564.8</v>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>Комплект корпуса масляного фильтра с фильтром для роботизированной коробки передач DSG7 DQ500 (0BH).
 Подходит для автомобилей VAG с 7-ступенчатой мокрой DSG DQ500.
@@ -7028,67 +7181,18 @@
 Рекомендуется при обслуживании и ремонте DSG 7 DQ500.</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="78" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>DQ500</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>3850</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="K73" s="2" t="n"/>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
-        </is>
-      </c>
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>DQ500-a-1.png, DQ500_a-2.png, DQ500_1.png, DQ500_3.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="74" ht="78" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -7099,49 +7203,45 @@
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>979</v>
+        <v>3850</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1500</v>
+        <v>8000</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdq200</t>
-        </is>
-      </c>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7_1.jpg</t>
+          <t>DQ500-a-1.png, DQ500_a-2.png, DQ500_1.png, DQ500_3.png</t>
         </is>
       </c>
     </row>
     <row r="75" ht="78" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -7156,41 +7256,45 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>8890</v>
+        <v>979</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12000</v>
+        <v>1500</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw_1.jpg</t>
+          <t>Dq200dsg7_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="76" ht="78" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -7201,45 +7305,45 @@
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>3879</v>
+        <v>8890</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Dq500_1.jpg, Dq500_2.png</t>
+          <t>Dq200dsg70am0cw_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="77" ht="78" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -7250,49 +7354,45 @@
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="n"/>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра двигателя EA888</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра двигателя EA888</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>4741</v>
+        <v>3879</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>6000</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>#корпусмасляногофильтраEA888</t>
-        </is>
-      </c>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>EA888_1.png</t>
+          <t>Dq500_1.jpg, Dq500_2.png</t>
         </is>
       </c>
     </row>
     <row r="78" ht="78" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -7307,41 +7407,45 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>6690</v>
+        <v>4741</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>#корпусмасляногофильтраEA888</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3_1.jpg</t>
+          <t>EA888_1.png</t>
         </is>
       </c>
     </row>
     <row r="79" ht="78" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -7352,45 +7456,45 @@
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>2366</v>
+        <v>6690</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
+          <t>EA888gen3_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="80" ht="78" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -7401,93 +7505,97 @@
       <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>100</v>
+        <v>2366</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>TEST001_2.jpg</t>
+          <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
         </is>
       </c>
     </row>
     <row r="81" ht="78" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr"/>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Тестовый товар не публикуется</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар — не публикуется</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="n"/>
-      <c r="I81" s="2" t="n"/>
-      <c r="J81" s="2" t="n"/>
-      <c r="K81" s="2" t="n">
+          <t>Тестовый товар не публикуется</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации</t>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>TESTWB001_2.jpg</t>
+          <t>TEST001_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="82" ht="78" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>TESTWB001</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -7497,43 +7605,35 @@
       <c r="E82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
-        </is>
-      </c>
+      <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="K82" s="2" t="n"/>
+          <t>Тестовый товар — не публикуется</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Тестовая карточка для проверки автоматизации</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>WHT001922_1.png</t>
+          <t>TESTWB001_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="83" ht="78" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -7541,46 +7641,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>1490</v>
+        <v>979</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="n"/>
+        <v>1500</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>690</v>
+      </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig_1.png</t>
+          <t>WHT001922_1.png</t>
         </is>
       </c>
     </row>
     <row r="84" ht="78" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -7595,39 +7703,39 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Новый оригинальный гидроаккумулятор VAG DSG7 DQ200</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>8890</v>
+        <v>1490</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="J84" s="2" t="n"/>
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig_3.png</t>
+          <t>filtr-setka-0b5-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="85" ht="78" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -7635,52 +7743,46 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
+          <t>Новый оригинальный гидроаккумулятор VAG DSG7 DQ200</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>12979</v>
+        <v>8890</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J85" s="2" t="n"/>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>jf011e_1.jpg</t>
+          <t>gidroakkumulyator-orig_3.png</t>
         </is>
       </c>
     </row>
     <row r="86" ht="78" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -7688,46 +7790,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>950</v>
+        <v>12979</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J86" s="2" t="n"/>
-      <c r="K86" s="2" t="n"/>
+        <v>15000</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>15000</v>
+      </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht_1.png</t>
+          <t>jf011e_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="87" ht="78" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -7738,43 +7848,43 @@
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>3879</v>
+        <v>950</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="J87" s="2" t="n"/>
       <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
+          <t>klipsy-shtokov-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="88" ht="78" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -7789,41 +7899,39 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>990</v>
+        <v>3879</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="J88" s="2" t="n"/>
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
+          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>nakladki-pedali_1.png, nakladki-pedali_2.png</t>
+          <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
         </is>
       </c>
     </row>
     <row r="89" ht="78" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -7834,43 +7942,45 @@
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>2890</v>
+        <v>990</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J89" s="2" t="n"/>
+        <v>1500</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht_1.png</t>
+          <t>nakladki-pedali_1.png, nakladki-pedali_2.png</t>
         </is>
       </c>
     </row>
     <row r="90" ht="78" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -7885,43 +7995,39 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200 без</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>990</v>
+        <v>2890</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="J90" s="2" t="n"/>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
-        </is>
-      </c>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig_1.png</t>
+          <t>planka-solenoid-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="91" ht="78" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -7936,39 +8042,43 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200 без</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>7500</v>
+        <v>990</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="J91" s="2" t="n"/>
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr_1.png</t>
+          <t>plastiny-solenoid-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="92" ht="78" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -7983,16 +8093,16 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>8500</v>
+        <v>7500</v>
       </c>
       <c r="I92" s="2" t="n">
         <v>12000</v>
@@ -8001,21 +8111,21 @@
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki_1.png</t>
+          <t>plita-filtr_1.png</t>
         </is>
       </c>
     </row>
     <row r="93" ht="78" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -8030,39 +8140,39 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
         <v>8500</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="J93" s="2" t="n"/>
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig_1.png</t>
+          <t>plita-filtr-pylniki_1.png</t>
         </is>
       </c>
     </row>
     <row r="94" ht="78" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -8077,16 +8187,16 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="I94" s="2" t="n">
         <v>13000</v>
@@ -8095,21 +8205,21 @@
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal_1.png</t>
+          <t>plita-filtr-pylniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="95" ht="78" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -8120,43 +8230,43 @@
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="J95" s="2" t="n"/>
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
+          <t>plita-filtr-pylniki-sal_1.png</t>
         </is>
       </c>
     </row>
     <row r="96" ht="78" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -8167,20 +8277,20 @@
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="I96" s="2" t="n">
         <v>12000</v>
@@ -8189,21 +8299,21 @@
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-v2_1.png</t>
+          <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="97" ht="78" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -8218,39 +8328,39 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>9500</v>
+        <v>7500</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="J97" s="2" t="n"/>
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig_1.png</t>
+          <t>plita-filtr-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="98" ht="78" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -8265,12 +8375,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Усиленная гидроплита + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
@@ -8290,14 +8400,14 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2_1.png</t>
+          <t>plita-pylniki-salniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="99" ht="78" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -8308,43 +8418,43 @@
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Усиленная гидроплита + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>1240</v>
+        <v>9500</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1500</v>
+        <v>13500</v>
       </c>
       <c r="J99" s="2" t="n"/>
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6_1.png, podshipnik-vilki-6_2.png</t>
+          <t>plita-pylniki-salniki-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="100" ht="78" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -8355,43 +8465,43 @@
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 крышки</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>3990</v>
+        <v>1240</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>6500</v>
+        <v>1500</v>
       </c>
       <c r="J100" s="2" t="n"/>
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki_1.png</t>
+          <t>podshipnik-vilki-6_1.png, podshipnik-vilki-6_2.png</t>
         </is>
       </c>
     </row>
     <row r="101" ht="78" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -8406,12 +8516,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 крышки</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 крышки</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
@@ -8431,14 +8541,14 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2_1.png</t>
+          <t>porshni-usil-pylniki-kryshki_1.png</t>
         </is>
       </c>
     </row>
     <row r="102" ht="78" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -8453,39 +8563,39 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 крышки</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>1850</v>
+        <v>3990</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>3000</v>
+        <v>6500</v>
       </c>
       <c r="J102" s="2" t="n"/>
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig_1.png</t>
+          <t>porshni-usil-pylniki-kryshki-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="103" ht="78" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -8500,12 +8610,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
@@ -8525,14 +8635,14 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2_1.png</t>
+          <t>pylniki-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="104" ht="78" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -8547,39 +8657,39 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>2850</v>
+        <v>1850</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="J104" s="2" t="n"/>
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig_1.png</t>
+          <t>pylniki-shtokov-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="105" ht="78" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -8594,12 +8704,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DQ200 DSG7</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DSG7 DQ200</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
@@ -8619,14 +8729,14 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2_1.png</t>
+          <t>remkomplekt-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="106" ht="78" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -8637,43 +8747,43 @@
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DQ200 DSG7</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>1490</v>
+        <v>2850</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="J106" s="2" t="n"/>
       <c r="K106" s="2" t="n"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig_1.png, salnik-shtoka-orig_2.png</t>
+          <t>remkomplekt-shtokov-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="107" ht="78" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -8684,16 +8794,16 @@
       <c r="C107" s="2" t="inlineStr"/>
       <c r="D107" s="2" t="n"/>
       <c r="E107" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
@@ -8713,14 +8823,14 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2_1.png</t>
+          <t>salnik-shtoka-orig_1.png, salnik-shtoka-orig_2.png</t>
         </is>
       </c>
     </row>
     <row r="108" ht="78" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -8731,43 +8841,43 @@
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с 4 шт DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>2490</v>
+        <v>1490</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="J108" s="2" t="n"/>
       <c r="K108" s="2" t="n"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr"/>
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum_1.png, salnik-tolkatelya-alum_2.png</t>
+          <t>salnik-shtoka-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="109" ht="78" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -8778,43 +8888,43 @@
       <c r="C109" s="2" t="inlineStr"/>
       <c r="D109" s="2" t="n"/>
       <c r="E109" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленные алюминиевые сальники толкателя с 4 шт DSG7 DQ200</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>1690</v>
+        <v>2490</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2800</v>
+        <v>4500</v>
       </c>
       <c r="J109" s="2" t="n"/>
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr"/>
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht_1.png</t>
+          <t>salnik-tolkatelya-alum_1.png, salnik-tolkatelya-alum_2.png</t>
         </is>
       </c>
     </row>
     <row r="110" ht="78" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -8829,39 +8939,39 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1890</v>
+        <v>1690</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J110" s="2" t="n"/>
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig_1.png</t>
+          <t>salniki-shtokov-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="111" ht="78" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -8872,20 +8982,20 @@
       <c r="C111" s="2" t="inlineStr"/>
       <c r="D111" s="2" t="n"/>
       <c r="E111" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок DSG7 DQ200 4 шт</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>1950</v>
+        <v>1890</v>
       </c>
       <c r="I111" s="2" t="n">
         <v>3000</v>
@@ -8894,21 +9004,21 @@
       <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr"/>
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht_1.png, salniki-tolkatelya-4sht_2.png</t>
+          <t>salniki-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="112" ht="78" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -8919,43 +9029,43 @@
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Полный комплект сальников толкателей вилок DSG7 DQ200 4 шт</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>999</v>
+        <v>1950</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1700</v>
+        <v>3000</v>
       </c>
       <c r="J112" s="2" t="n"/>
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr"/>
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-l_1.png</t>
+          <t>salniki-tolkatelya-4sht_1.png, salniki-tolkatelya-4sht_2.png</t>
         </is>
       </c>
     </row>
     <row r="113" ht="78" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -8970,12 +9080,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
@@ -8988,21 +9098,21 @@
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr"/>
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-r_1.png</t>
+          <t>salnikprivod-l_1.png</t>
         </is>
       </c>
     </row>
     <row r="114" ht="78" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -9017,12 +9127,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
@@ -9035,21 +9145,21 @@
       <c r="K114" s="2" t="n"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr"/>
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>salnikvhod_1.png</t>
+          <t>salnikprivod-r_1.png</t>
         </is>
       </c>
     </row>
     <row r="115" ht="78" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -9064,12 +9174,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
@@ -9082,21 +9192,21 @@
       <c r="K115" s="2" t="n"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr"/>
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>salnikvihod_1.png</t>
+          <t>salnikvhod_1.png</t>
         </is>
       </c>
     </row>
     <row r="116" ht="78" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -9111,39 +9221,39 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>1950</v>
+        <v>999</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3500</v>
+        <v>1700</v>
       </c>
       <c r="J116" s="2" t="n"/>
       <c r="K116" s="2" t="n"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr"/>
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity_1.png</t>
+          <t>salnikvihod_1.png</t>
         </is>
       </c>
     </row>
     <row r="117" ht="78" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -9158,39 +9268,39 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>7400</v>
+        <v>1950</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="J117" s="2" t="n"/>
       <c r="K117" s="2" t="n"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr"/>
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4_1.png</t>
+          <t>stalnaya-vstavka-plity_1.png</t>
         </is>
       </c>
     </row>
     <row r="118" ht="78" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -9205,39 +9315,39 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>усиленные алюминиевые сальники DSG7 DQ200, комплект 4 + 4</t>
+          <t>4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>8900</v>
+        <v>7400</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="J118" s="2" t="n"/>
       <c r="K118" s="2" t="n"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr"/>
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt_1.png</t>
+          <t>tolkateli-4-salniki-4_1.png</t>
         </is>
       </c>
     </row>
     <row r="119" ht="78" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -9252,30 +9362,77 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>усиленные алюминиевые сальники DSG7 DQ200, комплект 4 + 4</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>4990</v>
+        <v>8900</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="J119" s="2" t="n"/>
       <c r="K119" s="2" t="n"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr"/>
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="78" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>4990</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J120" s="2" t="n"/>
+      <c r="K120" s="2" t="n"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
         <is>
           <t>vtulki-shtokov-2sht_1.png</t>
         </is>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нераспознанные фото" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Товары" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Нераспознанные фото" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -171,13 +171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -196,13 +196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -221,13 +221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -246,13 +246,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -271,13 +271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -296,13 +296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -321,13 +321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -346,13 +346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -371,13 +371,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -396,13 +396,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -421,13 +421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -446,13 +446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -471,13 +471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -496,13 +496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -521,13 +521,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -546,13 +546,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -571,13 +571,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -596,13 +596,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -621,13 +621,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -646,13 +646,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -671,13 +671,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -696,13 +696,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -721,13 +721,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -746,13 +746,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -771,13 +771,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -796,13 +796,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -821,13 +821,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -846,13 +846,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -871,13 +871,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -896,13 +896,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -921,13 +921,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -946,13 +946,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -971,13 +971,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -996,13 +996,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1021,13 +1021,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1046,13 +1046,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1071,13 +1071,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1096,22 +1096,22 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>47</row>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1121,13 +1121,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1146,13 +1146,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1171,13 +1171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1196,13 +1196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1221,13 +1221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1246,13 +1246,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1271,13 +1271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1296,13 +1296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1321,13 +1321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1346,13 +1346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1371,13 +1371,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1396,13 +1396,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1421,13 +1421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1446,13 +1446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1471,13 +1471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1496,13 +1496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1521,13 +1521,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1546,13 +1546,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1571,22 +1571,22 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>67</row>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1596,13 +1596,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1621,13 +1621,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1646,13 +1646,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1671,22 +1671,22 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>73</row>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -1696,13 +1696,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1721,13 +1721,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1746,13 +1746,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1771,13 +1771,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1796,13 +1796,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1821,13 +1821,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1846,13 +1846,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1871,13 +1871,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1896,13 +1896,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1921,13 +1921,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1946,13 +1946,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1971,13 +1971,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1996,13 +1996,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2021,13 +2021,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2046,13 +2046,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2071,13 +2071,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2096,13 +2096,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2121,13 +2121,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2146,13 +2146,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2171,13 +2171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2196,13 +2196,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2221,13 +2221,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2246,13 +2246,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2271,13 +2271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2296,13 +2296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2321,13 +2321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2346,13 +2346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2371,13 +2371,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2396,13 +2396,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2421,13 +2421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2446,13 +2446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2471,13 +2471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2496,13 +2496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2521,13 +2521,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2546,13 +2546,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2571,13 +2571,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2596,13 +2596,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2621,13 +2621,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2646,13 +2646,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2671,13 +2671,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2696,13 +2696,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2721,13 +2721,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2746,13 +2746,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2771,13 +2771,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId105"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2796,13 +2796,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId106"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2821,13 +2821,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId107"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2846,13 +2846,38 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip cstate="print" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>120</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -3149,7 +3174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3315,7 +3340,7 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -3346,7 +3371,7 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>02E 305 045_1.png, 02E 305 045_2.png, 02E 305 045_3.png</t>
+          <t>02E 305 045_1.png</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4128,7 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0AM325473_1.png, 0AM325473_1.jpg</t>
+          <t>0AM325473_1.jpg, 0AM325473_1.png</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4344,7 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0BH325_1.jpg, 0BH325_1.png, 0BH325_2.png, 0BH325_3.png</t>
+          <t>0BH325_1.png, 0BH325_1.jpg, 0BH325_2.png, 0BH325_3.png</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4810,7 @@
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -4820,7 +4845,7 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0am325025H-1.png, 0am325025H_2.png, 0am325025H_3.png, 0am325025H_4.jpg</t>
+          <t>0am325025H-1.png, 0am325025H_2.png, 0am325025H_4.jpg</t>
         </is>
       </c>
     </row>
@@ -5179,11 +5204,7 @@
           <t>0am325025h</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -5193,45 +5214,45 @@
       <c r="E37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
-        </is>
-      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>1990</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>93</v>
-      </c>
+          <t>Комплект штока мехатроника DSG7 DQ200 сальник пыльник крышка</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n">
         <v>4160</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
+          <t>Более 5 лет мы продаём ремкомплект с максимально усиленной плитой и собираем блоки только на нем. Решите проблему давления в мехатронике раз и навсегда. 100% качество.
+Качественный сплав — усиленная гидроплита держит давление (смотрите видео).
+Все необходимые прокладки в ремкомплекте:
+Прокладка поддона
+Фильтр мехатроника 0AM325433E, 0AM325433B
+Пыльники штоков сцепления DSG7 DQ200 0AM, 0CW, 0AM325091F, 0AM325091E
+И так далее.
+Покупая наш ремонтный комплект гидроблока DSG7 0AM/0CW, вы выполняете полноценный ремонт мехатроника, меняя все расходники и устанавливая новую усиленную гидроплиту 0AM325066AE.
+Ошибки: P17BF, P189C, P0841, P1895
+Артикулы: 0AM325025D; 0AM325025DX; 0AM325025H; 0AM325025HX; 0AM325025L; 0AM325025LX; 0AM325025M; 0AM325025MX; 0AM325025K; 0AM325025N; 0AM325025R; 0AM325026A; 0AM325026C; 0AM325025DZSN; 0AM325025DZEM.
+Заказывайте!</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>фото уже на карточке Ozon, локального файла нет: https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="78" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5239,58 +5260,46 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>2879</v>
+        <v>1990</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>1950</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
-        </is>
-      </c>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0am325025j_1.png</t>
+          <t>0am325025hfe_1.png, 0am325025hfe_2.png</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -5309,43 +5318,47 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1490</v>
+        <v>2879</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2300</v>
+        <v>5000</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1325</v>
+        <v>1950</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0am325025l.png</t>
+          <t>0am325025j_1.png</t>
         </is>
       </c>
     </row>
     <row r="40" ht="78" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -5364,43 +5377,43 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8879</v>
+        <v>1490</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12000</v>
+        <v>2300</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>8443.5</v>
+        <v>1325</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
+          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0am325025m.png</t>
+          <t>0am325025l.png</t>
         </is>
       </c>
     </row>
     <row r="41" ht="78" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -5419,43 +5432,43 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>8979</v>
+        <v>8879</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>12000</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>8378.5</v>
+        <v>8443.5</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0am325025n_1.jpg</t>
+          <t>0am325025m.png</t>
         </is>
       </c>
     </row>
     <row r="42" ht="78" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -5474,43 +5487,43 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>979</v>
+        <v>8979</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1800</v>
+        <v>12000</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>980</v>
+        <v>8378.5</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0am325025q_1.png</t>
+          <t>0am325025n_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="43" ht="78" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -5529,43 +5542,43 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1479</v>
+        <v>979</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1475</v>
+        <v>980</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0am325025r_1.png</t>
+          <t>0am325025q_1.png</t>
         </is>
       </c>
     </row>
     <row r="44" ht="78" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -5584,43 +5597,43 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный длинный шток 0AM325091E + DSG7 DQ200</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>4490</v>
+        <v>1479</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>3430</v>
+        <v>1475</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0am325025u_1.png</t>
+          <t>0am325025r_1.png</t>
         </is>
       </c>
     </row>
     <row r="45" ht="78" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -5628,52 +5641,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+          <t>Ремкомплект Усиленный длинный шток 0AM325091E + DSG7 DQ200</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>78475</v>
+        <v>4490</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>90000</v>
+        <v>6000</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2" t="n"/>
+        <v>82</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>3430</v>
+      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
-        </is>
-      </c>
+          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0am325025x_1.jpg</t>
+          <t>0am325025u_1.png</t>
         </is>
       </c>
     </row>
     <row r="46" ht="78" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -5681,57 +5696,59 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный короткий шток 0AM325091F + DSG7 DQ200</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>4490</v>
+        <v>78475</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6000</v>
+        <v>90000</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>3430</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0am325025z.png</t>
+          <t>0am325025x_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="47" ht="78" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>0am325025ze</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr"/>
+          <t>0am325025z</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -5739,21 +5756,72 @@
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект Усиленный короткий шток 0AM325091F + DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>4490</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>3430</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0am325025z.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="78" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>0am325025ze</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DQ200 DSG7 0AM Новые соленоиды Bosch</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n">
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n">
         <v>69302.22</v>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Абсолютно новый мехатроник DSG7 DQ200 (0AM / 0CW) — гидравлическая часть
 В продаже полностью восстановленный до состояния нового мехатроник DSG7 DQ200 для коробок передач 0AM и 0CW. Узел собран с использованием новых оригинальных и OEM-компонентов, прошёл обязательную проверку и готов к установке.
@@ -5794,73 +5862,18 @@
 Капитальном ремонте коробки DQ200</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="78" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>0am325025С</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>980</v>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
-        </is>
-      </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0am325025С_1.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="78" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -5879,43 +5892,43 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1479</v>
+        <v>979</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1325</v>
+        <v>980</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0am325066AC_1.png</t>
+          <t>0am325025С_1.png</t>
         </is>
       </c>
     </row>
     <row r="50" ht="78" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -5930,47 +5943,47 @@
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>979</v>
+        <v>1479</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>980</v>
+        <v>1325</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad_1.png, 0am325066ad_1.jpg</t>
+          <t>0am325066AC_1.png</t>
         </is>
       </c>
     </row>
     <row r="51" ht="78" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -5989,43 +6002,43 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>8879</v>
+        <v>979</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>7347.3</v>
+        <v>980</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae_1.png, 0am325066ae_4.png</t>
+          <t>0am325066ad_1.jpg, 0am325066ad_1.png</t>
         </is>
       </c>
     </row>
     <row r="52" ht="78" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -6040,51 +6053,47 @@
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>2879</v>
+        <v>8879</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2850</v>
+        <v>7347.3</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dsg7</t>
-        </is>
-      </c>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0am325091e.png</t>
+          <t>0am325066ae_1.png, 0am325066ae_4.png</t>
         </is>
       </c>
     </row>
     <row r="53" ht="78" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -6092,32 +6101,40 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>8850</v>
+        <v>2879</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
+        <v>5000</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>2850</v>
+      </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
+          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6128,14 +6145,14 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0am325091e-set_1.png</t>
+          <t>0am325091e.png</t>
         </is>
       </c>
     </row>
     <row r="54" ht="78" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6143,54 +6160,50 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм 0AM325091F</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 DSG7 DQ200</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>2879</v>
+        <v>8850</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>2950</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0am325091f.png</t>
+          <t>0am325091e-set_1.png</t>
         </is>
       </c>
     </row>
     <row r="55" ht="78" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6198,46 +6211,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм 0AM325091F</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>8850</v>
+        <v>2879</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="n"/>
+        <v>5000</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>2950</v>
+      </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0am325091f-set_1.png</t>
+          <t>0am325091f.png</t>
         </is>
       </c>
     </row>
     <row r="56" ht="78" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6245,54 +6266,46 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 DSG7 DQ200</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>2479</v>
+        <v>8850</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>2447.15</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae_1.png</t>
+          <t>0am325091f-set_1.png</t>
         </is>
       </c>
     </row>
     <row r="57" ht="78" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6300,48 +6313,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200 10 шт оригинал</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>11979</v>
+        <v>2479</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2447.15</v>
+      </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0ambset_1.png, 0ambset_2.png</t>
+          <t>0am325477ae_1.png</t>
         </is>
       </c>
     </row>
     <row r="58" ht="78" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6356,45 +6375,41 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200 10 шт оригинал</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>931</v>
+        <v>11979</v>
       </c>
       <c r="I58" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J58" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>49</v>
       </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdsg7dq200</t>
-        </is>
-      </c>
+          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0cw0am_1.jpg, 0cw0am_1.png</t>
+          <t>0ambset_1.png, 0ambset_2.png</t>
         </is>
       </c>
     </row>
     <row r="59" ht="78" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -6405,49 +6420,49 @@
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>16890</v>
+        <v>931</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкиdq200</t>
+          <t>#Прокладкаdsg7dq200</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025.png, 0cw0am325025_1.png, 0cw0am325025-2.png</t>
+          <t>0cw0am_1.png, 0cw0am_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="60" ht="78" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6458,49 +6473,49 @@
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>850</v>
+        <v>16890</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1500</v>
+        <v>25000</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкаdq200dsg</t>
+          <t>#Прокладкиdq200</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200_1.jpg</t>
+          <t>0cw0am325025.png, 0cw0am325025_1.png, 0cw0am325025-2.png</t>
         </is>
       </c>
     </row>
     <row r="61" ht="78" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -6515,45 +6530,45 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы DSG7 DQ200 0AM927769N</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1290</v>
+        <v>850</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+          <t>#Прокладкаdq200dsg</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0cw325025h_1.png</t>
+          <t>0cw0amdsgdq200_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="62" ht="78" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -6564,45 +6579,49 @@
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Прокладка электронной платы DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1490</v>
+        <v>1290</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0сц_1.png, 0сц_2.png, 0сц_3.png, 0сц_4.png, 0сц_5.png, 0сц_6.png, 0сц_7.png</t>
+          <t>0cw325025h_1.png</t>
         </is>
       </c>
     </row>
     <row r="63" ht="78" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -6610,54 +6629,48 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>979</v>
+        <v>1490</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>980</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>122390AK-AF_1.jpg, 122390AK-AF_1.png</t>
+          <t>0сц_1.png, 0сц_2.png, 0сц_3.png, 0сц_4.png, 0сц_5.png, 0сц_6.png, 0сц_7.png</t>
         </is>
       </c>
     </row>
     <row r="64" ht="78" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -6672,47 +6685,47 @@
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1490</v>
+        <v>979</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1319.7</v>
+        <v>980</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>122390AKAF_1.png</t>
+          <t>122390AK-AF_1.png, 122390AK-AF_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="65" ht="78" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -6727,47 +6740,47 @@
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1479</v>
+        <v>1490</v>
       </c>
       <c r="I65" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1225</v>
+        <v>1319.7</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>123014‑AF_1.png, 123014‑AF_2.png</t>
+          <t>122390AKAF_1.png</t>
         </is>
       </c>
     </row>
     <row r="66" ht="78" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -6782,54 +6795,54 @@
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>58900</v>
+        <v>1479</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>80000</v>
+        <v>2500</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>40052</v>
+        <v>1225</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>#гидроблокjf011e</t>
-        </is>
-      </c>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>31705-1XF0C_1.jpg</t>
+          <t>123014‑AF_1.png, 123014‑AF_2.png</t>
         </is>
       </c>
     </row>
     <row r="67" ht="78" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr"/>
+          <t>31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -6837,21 +6850,76 @@
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>58900</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок JF011E Старое поколение Nissan Mitsubishi Renault</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
       <c r="K67" s="2" t="n">
         <v>40052</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf011e</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>31705-1XF0C_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="78" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>31705-1XF1A</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок JF011E Старое поколение Nissan Mitsubishi Renault</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n">
+        <v>40052</v>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E Старое поколение для вариатора CVT RE0F10A. Восстанавливает давление масла и стабильную работу трансмиссии. Прямая замена штатного узла без доработок.
 Гидроблок вариатора JF011E Старое поколение — управляющий узел CVT-коробки, отвечающий за распределение давления масла и работу соленоидов. Применяется в вариаторах RE0F10A и устанавливается на автомобили Nissan, Mitsubishi, Renault и Jeep.
@@ -6879,77 +6947,18 @@
 гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi ремонт вариатора jf011e</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr"/>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="78" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>58900</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>80000</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>42408</v>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
-        </is>
-      </c>
+      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>31705-X428B_1.png, 31705-X428B_2.png, 31705-X428B_3.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="69" ht="78" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -6964,16 +6973,16 @@
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
@@ -6983,28 +6992,32 @@
         <v>80000</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>40052</v>
+        <v>42408</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>317053TX0C_1.png</t>
+          <t>31705-X428B_1.png, 31705-X428B_2.png, 31705-X428B_3.png</t>
         </is>
       </c>
     </row>
     <row r="70" ht="78" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -7023,43 +7036,43 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>999</v>
+        <v>58900</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2000</v>
+        <v>80000</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>980</v>
+        <v>40052</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>55565480_1.png</t>
+          <t>317053TX0C_1.png</t>
         </is>
       </c>
     </row>
     <row r="71" ht="78" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -7067,88 +7080,101 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>19800</v>
+        <v>999</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="n"/>
+        <v>2000</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>980</v>
+      </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>6t30_1.png</t>
+          <t>55565480_1.png</t>
         </is>
       </c>
     </row>
     <row r="72" ht="78" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>DF-DQ250-ALU-KIT</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>6t30</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045+масляный фильтр DSG6</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>19800</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>25000</v>
+      </c>
       <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="n">
-        <v>2150</v>
-      </c>
+      <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
-Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>6t30_1.png</t>
         </is>
       </c>
     </row>
     <row r="73" ht="78" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>DF-DQ500-FH-KIT</t>
+          <t>DF-DQ250-ALU-KIT</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
@@ -7164,16 +7190,58 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + масляный фильтр DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра DSG6 DQ250 02E305045+масляный фильтр DSG6</t>
         </is>
       </c>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
       <c r="J73" s="2" t="n"/>
       <c r="K73" s="2" t="n">
+        <v>2150</v>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
+Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>(нет фото ни локально, ни на карточке)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="78" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>DF-DQ500-FH-KIT</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + масляный фильтр DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="n">
         <v>1564.8</v>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>Комплект корпуса масляного фильтра с фильтром для роботизированной коробки передач DSG7 DQ500 (0BH).
 Подходит для автомобилей VAG с 7-ступенчатой мокрой DSG DQ500.
@@ -7181,67 +7249,18 @@
 Рекомендуется при обслуживании и ремонте DSG 7 DQ500.</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr"/>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="78" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>DQ500</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>3850</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="K74" s="2" t="n"/>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
-        </is>
-      </c>
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>DQ500-a-1.png, DQ500_a-2.png, DQ500_1.png, DQ500_3.png</t>
+          <t>(нет фото ни локально, ни на карточке)</t>
         </is>
       </c>
     </row>
     <row r="75" ht="78" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -7252,49 +7271,45 @@
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>979</v>
+        <v>3850</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1500</v>
+        <v>8000</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdq200</t>
-        </is>
-      </c>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7_1.jpg</t>
+          <t>DQ500-a-1.png, DQ500_a-2.png, DQ500_1.png, DQ500_3.png</t>
         </is>
       </c>
     </row>
     <row r="76" ht="78" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -7309,41 +7324,45 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>8890</v>
+        <v>979</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>12000</v>
+        <v>1500</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw_1.jpg</t>
+          <t>Dq200dsg7_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="77" ht="78" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -7354,45 +7373,45 @@
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="n"/>
       <c r="E77" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>3879</v>
+        <v>8890</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Dq500_1.jpg, Dq500_2.png</t>
+          <t>Dq200dsg70am0cw_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="78" ht="78" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -7403,49 +7422,45 @@
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра двигателя EA888</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра двигателя EA888</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>4741</v>
+        <v>3879</v>
       </c>
       <c r="I78" s="2" t="n">
         <v>6000</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>#корпусмасляногофильтраEA888</t>
-        </is>
-      </c>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>EA888_1.png</t>
+          <t>Dq500_1.jpg, Dq500_2.png</t>
         </is>
       </c>
     </row>
     <row r="79" ht="78" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -7460,41 +7475,45 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>6690</v>
+        <v>4741</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>#корпусмасляногофильтраEA888</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3_1.jpg</t>
+          <t>EA888_1.png</t>
         </is>
       </c>
     </row>
     <row r="80" ht="78" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -7505,45 +7524,45 @@
       <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>2366</v>
+        <v>6690</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
+          <t>EA888gen3_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="81" ht="78" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -7554,93 +7573,97 @@
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>100</v>
+        <v>2366</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>TEST001_2.jpg</t>
+          <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
         </is>
       </c>
     </row>
     <row r="82" ht="78" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Тестовый товар не публикуется</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар — не публикуется</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
-      <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="n">
+          <t>Тестовый товар не публикуется</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации</t>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>TESTWB001_2.jpg</t>
+          <t>TEST001_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="83" ht="78" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>TESTWB001</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -7650,45 +7673,35 @@
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
-        </is>
-      </c>
+      <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>93</v>
-      </c>
+          <t>Тестовый товар — не публикуется</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
       <c r="K83" s="2" t="n">
-        <v>690</v>
+        <v>100</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Тестовая карточка для проверки автоматизации</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>WHT001922_1.png</t>
+          <t>TESTWB001_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="84" ht="78" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -7696,46 +7709,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1490</v>
+        <v>979</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="n"/>
+        <v>1500</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>690</v>
+      </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig_1.png</t>
+          <t>WHT001922_1.png</t>
         </is>
       </c>
     </row>
     <row r="85" ht="78" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -7750,39 +7771,39 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Новый оригинальный гидроаккумулятор VAG DSG7 DQ200</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>8890</v>
+        <v>1490</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="J85" s="2" t="n"/>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig_3.png</t>
+          <t>filtr-setka-0b5-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="86" ht="78" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -7790,54 +7811,46 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
+          <t>Новый оригинальный гидроаккумулятор VAG DSG7 DQ200</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>12979</v>
+        <v>8890</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>15000</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>jf011e_1.jpg</t>
+          <t>gidroakkumulyator-orig_3.png</t>
         </is>
       </c>
     </row>
     <row r="87" ht="78" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -7845,46 +7858,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>950</v>
+        <v>12979</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J87" s="2" t="n"/>
-      <c r="K87" s="2" t="n"/>
+        <v>15000</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>15000</v>
+      </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht_1.png</t>
+          <t>jf011e_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="88" ht="78" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -7895,43 +7916,43 @@
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>3879</v>
+        <v>950</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="J88" s="2" t="n"/>
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
+          <t>klipsy-shtokov-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="89" ht="78" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -7946,41 +7967,39 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>990</v>
+        <v>3879</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="J89" s="2" t="n"/>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
+          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>nakladki-pedali_1.png, nakladki-pedali_2.png</t>
+          <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
         </is>
       </c>
     </row>
     <row r="90" ht="78" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -7991,43 +8010,45 @@
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>2890</v>
+        <v>990</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J90" s="2" t="n"/>
+        <v>1500</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht_1.png</t>
+          <t>nakladki-pedali_1.png, nakladki-pedali_2.png</t>
         </is>
       </c>
     </row>
     <row r="91" ht="78" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -8042,43 +8063,39 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200 без</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>990</v>
+        <v>2890</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="J91" s="2" t="n"/>
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
-        </is>
-      </c>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig_1.png</t>
+          <t>planka-solenoid-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="92" ht="78" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -8093,39 +8110,43 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200 без</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>7500</v>
+        <v>990</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="J92" s="2" t="n"/>
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr_1.png</t>
+          <t>plastiny-solenoid-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="93" ht="78" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -8140,16 +8161,16 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>8500</v>
+        <v>7500</v>
       </c>
       <c r="I93" s="2" t="n">
         <v>12000</v>
@@ -8158,21 +8179,21 @@
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki_1.png</t>
+          <t>plita-filtr_1.png</t>
         </is>
       </c>
     </row>
     <row r="94" ht="78" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -8187,39 +8208,39 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
         <v>8500</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="J94" s="2" t="n"/>
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig_1.png</t>
+          <t>plita-filtr-pylniki_1.png</t>
         </is>
       </c>
     </row>
     <row r="95" ht="78" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -8234,16 +8255,16 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="I95" s="2" t="n">
         <v>13000</v>
@@ -8252,21 +8273,21 @@
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal_1.png</t>
+          <t>plita-filtr-pylniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="96" ht="78" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -8277,43 +8298,43 @@
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="J96" s="2" t="n"/>
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
+          <t>plita-filtr-pylniki-sal_1.png</t>
         </is>
       </c>
     </row>
     <row r="97" ht="78" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -8324,20 +8345,20 @@
       <c r="C97" s="2" t="inlineStr"/>
       <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="I97" s="2" t="n">
         <v>12000</v>
@@ -8346,21 +8367,21 @@
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-v2_1.png</t>
+          <t>plita-filtr-salniki-orig.png, plita-filtr-salniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="98" ht="78" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -8375,39 +8396,39 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>9500</v>
+        <v>7500</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="J98" s="2" t="n"/>
       <c r="K98" s="2" t="n"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig_1.png</t>
+          <t>plita-filtr-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="99" ht="78" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -8422,12 +8443,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Усиленная гидроплита + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
@@ -8447,14 +8468,14 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2_1.png</t>
+          <t>plita-pylniki-salniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="100" ht="78" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -8465,43 +8486,43 @@
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Усиленная гидроплита + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>1240</v>
+        <v>9500</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1500</v>
+        <v>13500</v>
       </c>
       <c r="J100" s="2" t="n"/>
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6_1.png, podshipnik-vilki-6_2.png</t>
+          <t>plita-pylniki-salniki-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="101" ht="78" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -8512,43 +8533,43 @@
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="n"/>
       <c r="E101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 крышки</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>3990</v>
+        <v>1240</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>6500</v>
+        <v>1500</v>
       </c>
       <c r="J101" s="2" t="n"/>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki_1.png</t>
+          <t>podshipnik-vilki-6_1.png, podshipnik-vilki-6_2.png</t>
         </is>
       </c>
     </row>
     <row r="102" ht="78" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -8563,12 +8584,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 крышки</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 крышки</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
@@ -8588,14 +8609,14 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2_1.png</t>
+          <t>porshni-usil-pylniki-kryshki_1.png</t>
         </is>
       </c>
     </row>
     <row r="103" ht="78" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -8610,39 +8631,39 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 крышки</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>1850</v>
+        <v>3990</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3000</v>
+        <v>6500</v>
       </c>
       <c r="J103" s="2" t="n"/>
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig_1.png</t>
+          <t>porshni-usil-pylniki-kryshki-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="104" ht="78" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -8657,12 +8678,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
@@ -8682,14 +8703,14 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2_1.png</t>
+          <t>pylniki-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="105" ht="78" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -8704,39 +8725,39 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>2850</v>
+        <v>1850</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="J105" s="2" t="n"/>
       <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig_1.png</t>
+          <t>pylniki-shtokov-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="106" ht="78" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -8751,12 +8772,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DQ200 DSG7</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DSG7 DQ200</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
@@ -8776,14 +8797,14 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2_1.png</t>
+          <t>remkomplekt-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="107" ht="78" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -8794,43 +8815,43 @@
       <c r="C107" s="2" t="inlineStr"/>
       <c r="D107" s="2" t="n"/>
       <c r="E107" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DQ200 DSG7</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>1490</v>
+        <v>2850</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="J107" s="2" t="n"/>
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig_1.png, salnik-shtoka-orig_2.png</t>
+          <t>remkomplekt-shtokov-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="108" ht="78" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -8841,16 +8862,16 @@
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
@@ -8870,14 +8891,14 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2_1.png</t>
+          <t>salnik-shtoka-orig_1.png, salnik-shtoka-orig_2.png</t>
         </is>
       </c>
     </row>
     <row r="109" ht="78" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -8888,43 +8909,43 @@
       <c r="C109" s="2" t="inlineStr"/>
       <c r="D109" s="2" t="n"/>
       <c r="E109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с 4 шт DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>2490</v>
+        <v>1490</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="J109" s="2" t="n"/>
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr"/>
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum_1.png, salnik-tolkatelya-alum_2.png</t>
+          <t>salnik-shtoka-orig-v2_1.png</t>
         </is>
       </c>
     </row>
     <row r="110" ht="78" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -8935,43 +8956,43 @@
       <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="n"/>
       <c r="E110" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленные алюминиевые сальники толкателя с 4 шт DSG7 DQ200</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1690</v>
+        <v>2490</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2800</v>
+        <v>4500</v>
       </c>
       <c r="J110" s="2" t="n"/>
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht_1.png</t>
+          <t>salnik-tolkatelya-alum_1.png, salnik-tolkatelya-alum_2.png</t>
         </is>
       </c>
     </row>
     <row r="111" ht="78" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -8986,39 +9007,39 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>1890</v>
+        <v>1690</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J111" s="2" t="n"/>
       <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr"/>
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig_1.png</t>
+          <t>salniki-shtokov-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="112" ht="78" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -9029,20 +9050,20 @@
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок DSG7 DQ200 4 шт</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>1950</v>
+        <v>1890</v>
       </c>
       <c r="I112" s="2" t="n">
         <v>3000</v>
@@ -9051,21 +9072,21 @@
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr"/>
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht_1.png, salniki-tolkatelya-4sht_2.png</t>
+          <t>salniki-shtokov-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="113" ht="78" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -9076,43 +9097,43 @@
       <c r="C113" s="2" t="inlineStr"/>
       <c r="D113" s="2" t="n"/>
       <c r="E113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Полный комплект сальников толкателей вилок DSG7 DQ200 4 шт</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>999</v>
+        <v>1950</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1700</v>
+        <v>3000</v>
       </c>
       <c r="J113" s="2" t="n"/>
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr"/>
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-l_1.png</t>
+          <t>salniki-tolkatelya-4sht_1.png, salniki-tolkatelya-4sht_2.png</t>
         </is>
       </c>
     </row>
     <row r="114" ht="78" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -9127,12 +9148,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
@@ -9145,21 +9166,21 @@
       <c r="K114" s="2" t="n"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr"/>
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-r_1.png</t>
+          <t>salnikprivod-l_1.png</t>
         </is>
       </c>
     </row>
     <row r="115" ht="78" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -9174,12 +9195,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
@@ -9192,21 +9213,21 @@
       <c r="K115" s="2" t="n"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr"/>
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>salnikvhod_1.png</t>
+          <t>salnikprivod-r_1.png</t>
         </is>
       </c>
     </row>
     <row r="116" ht="78" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -9221,12 +9242,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
@@ -9239,21 +9260,21 @@
       <c r="K116" s="2" t="n"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr"/>
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>salnikvihod_1.png</t>
+          <t>salnikvhod_1.png</t>
         </is>
       </c>
     </row>
     <row r="117" ht="78" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -9268,39 +9289,39 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>1950</v>
+        <v>999</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>3500</v>
+        <v>1700</v>
       </c>
       <c r="J117" s="2" t="n"/>
       <c r="K117" s="2" t="n"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr"/>
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity_1.png</t>
+          <t>salnikvihod_1.png</t>
         </is>
       </c>
     </row>
     <row r="118" ht="78" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -9315,39 +9336,39 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>7400</v>
+        <v>1950</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="J118" s="2" t="n"/>
       <c r="K118" s="2" t="n"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr"/>
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4_1.png</t>
+          <t>stalnaya-vstavka-plity_1.png</t>
         </is>
       </c>
     </row>
     <row r="119" ht="78" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -9362,39 +9383,39 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>усиленные алюминиевые сальники DSG7 DQ200, комплект 4 + 4</t>
+          <t>4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>8900</v>
+        <v>7400</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="J119" s="2" t="n"/>
       <c r="K119" s="2" t="n"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr"/>
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt_1.png</t>
+          <t>tolkateli-4-salniki-4_1.png</t>
         </is>
       </c>
     </row>
     <row r="120" ht="78" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -9409,30 +9430,77 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>усиленные алюминиевые сальники DSG7 DQ200, комплект 4 + 4</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>4990</v>
+        <v>8900</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="J120" s="2" t="n"/>
       <c r="K120" s="2" t="n"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr"/>
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="78" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>4990</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J121" s="2" t="n"/>
+      <c r="K121" s="2" t="n"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
         <is>
           <t>vtulki-shtokov-2sht_1.png</t>
         </is>

--- a/data/master_control.xlsx
+++ b/data/master_control.xlsx
@@ -836,17 +836,42 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
       <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -867,11 +892,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -892,11 +942,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -917,11 +967,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -942,11 +992,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -967,11 +1017,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -992,11 +1042,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1017,11 +1067,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1042,11 +1092,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1067,36 +1117,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1117,11 +1142,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1142,11 +1192,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1167,11 +1217,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,11 +1242,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,11 +1267,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,11 +1292,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,11 +1317,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId45"/>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,11 +1342,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId46"/>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,11 +1367,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId47"/>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1342,11 +1392,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId48"/>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1367,11 +1417,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1392,11 +1442,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1417,11 +1467,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId51"/>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1442,11 +1492,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId52"/>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1467,11 +1517,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId53"/>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1492,11 +1542,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId54"/>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1517,11 +1567,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId55"/>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1542,36 +1592,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId56"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId57"/>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1592,11 +1617,36 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId58"/>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1617,11 +1667,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId59"/>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1642,11 +1692,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1667,11 +1717,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1692,11 +1742,61 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId62"/>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1717,11 +1817,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1742,11 +1842,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1767,11 +1867,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1792,11 +1892,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1817,11 +1917,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1842,11 +1942,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId72"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1867,11 +1967,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1892,11 +1992,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId70"/>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1917,11 +2017,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId71"/>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId75"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1942,11 +2042,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId72"/>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId76"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1967,11 +2067,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId73"/>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1992,11 +2092,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId74"/>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2017,11 +2117,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId75"/>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2042,11 +2142,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId76"/>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2067,11 +2167,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2092,11 +2192,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2117,11 +2217,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId79"/>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2142,11 +2242,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId80"/>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2167,11 +2267,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId81"/>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2192,11 +2292,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId82"/>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2217,11 +2317,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2242,11 +2342,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2267,11 +2367,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2292,11 +2392,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2317,11 +2417,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2342,11 +2442,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2367,11 +2467,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2392,11 +2492,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId90"/>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2417,11 +2517,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId91"/>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2442,11 +2542,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId92"/>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2467,11 +2567,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId93"/>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2492,11 +2592,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId94"/>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2517,11 +2617,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2542,11 +2642,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId96"/>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2567,11 +2667,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2592,11 +2692,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2617,11 +2717,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2642,11 +2742,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2667,11 +2767,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId101"/>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId105"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2692,11 +2792,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="102" name="Image 102" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId106"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2717,11 +2817,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="103" name="Image 103" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId107"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2742,11 +2842,11 @@
     <ext cx="952500" cy="952500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="104" name="Image 104" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId108"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2762,106 +2862,6 @@
       <col>3</col>
       <colOff>0</colOff>
       <row>116</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="105" name="Image 105" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId105"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="106" name="Image 106" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId106"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="107" name="Image 107" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId107"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>119</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="108" name="Image 108" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="952500"/>
@@ -3174,7 +3174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3337,7 +3337,11 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -3361,7 +3365,9 @@
       <c r="J3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="K3" s="2" t="n"/>
+      <c r="K3" s="2" t="n">
+        <v>2100</v>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
@@ -3401,7 +3407,7 @@
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n">
-        <v>1800</v>
+        <v>1710</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -3540,7 +3546,7 @@
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -3573,7 +3579,7 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>02e305045_1.png, 02e305045_2.png, 02e305045_3.png, 02e305045_4.png</t>
+          <t>02e305045_1.png, 02e305045_2.png</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4813,11 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n">
         <v>3</v>
@@ -4831,7 +4841,9 @@
       <c r="J30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K30" s="2" t="n"/>
+      <c r="K30" s="2" t="n">
+        <v>85025</v>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
@@ -5026,10 +5038,14 @@
     <row r="34" ht="78" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr"/>
+          <t>0am325025ae</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -5037,57 +5053,51 @@
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
+          <t>усиленная прокладка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>4879</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>31</v>
+      </c>
       <c r="K34" s="2" t="n">
-        <v>85025</v>
+        <v>3920</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников (как на фото) Максимально профессиональное восстановление в заводских условиях + проверка на стенде = отличный результат и гарантия работоспособности.
-без электронной платы только гидравлика
-Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.
-Для каких автомобилей подходит
-Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) 
-Audi (A1, A3, TT, Q2 и др.) 
-Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)
-Почему часто нужен ремонт / замена мехатроника DQ200
-У блока DQ200 0AM/0CW есть типичные слабые места: 
-Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.
-Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.
-Типичные симптомы:
-ошибки давления (P17BF, P189C/P1895, P06293 и др.) 
-грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях 
-Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — готовый к установке блок (без электронной платы только гидравлика)
-Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).
-Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.
-Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. 
- Что входит:
-Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, штоки, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды..
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>0am325025ae_2.png</t>
         </is>
       </c>
     </row>
     <row r="35" ht="78" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -5106,47 +5116,43 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>усиленная прокладка мехатроника DSG7 DQ200</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>4879</v>
+        <v>3879</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>3920</v>
+        <v>4440</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
-        </is>
-      </c>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0am325025ae_2.png</t>
+          <t>0am325025f_1.png</t>
         </is>
       </c>
     </row>
     <row r="36" ht="78" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5161,50 +5167,52 @@
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3879</v>
+        <v>1990</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>43</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n">
-        <v>4440</v>
+        <v>4160</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0am325025f_1.png</t>
+          <t>0am325025hfe_1.png, 0am325025hfe_2.png</t>
         </is>
       </c>
     </row>
     <row r="37" ht="78" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>0am325025h</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr"/>
+          <t>0am325025j</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -5212,47 +5220,51 @@
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Комплект штока мехатроника DSG7 DQ200 сальник пыльник крышка</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
+          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>2879</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>88</v>
+      </c>
       <c r="K37" s="2" t="n">
-        <v>4160</v>
+        <v>1950</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Более 5 лет мы продаём ремкомплект с максимально усиленной плитой и собираем блоки только на нем. Решите проблему давления в мехатронике раз и навсегда. 100% качество.
-Качественный сплав — усиленная гидроплита держит давление (смотрите видео).
-Все необходимые прокладки в ремкомплекте:
-Прокладка поддона
-Фильтр мехатроника 0AM325433E, 0AM325433B
-Пыльники штоков сцепления DSG7 DQ200 0AM, 0CW, 0AM325091F, 0AM325091E
-И так далее.
-Покупая наш ремонтный комплект гидроблока DSG7 0AM/0CW, вы выполняете полноценный ремонт мехатроника, меняя все расходники и устанавливая новую усиленную гидроплиту 0AM325066AE.
-Ошибки: P17BF, P189C, P0841, P1895
-Артикулы: 0AM325025D; 0AM325025DX; 0AM325025H; 0AM325025HX; 0AM325025L; 0AM325025LX; 0AM325025M; 0AM325025MX; 0AM325025K; 0AM325025N; 0AM325025R; 0AM325026A; 0AM325026C; 0AM325025DZSN; 0AM325025DZEM.
-Заказывайте!</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>0am325025j_1.png</t>
         </is>
       </c>
     </row>
     <row r="38" ht="78" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5260,46 +5272,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1990</v>
+        <v>1490</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
+        <v>2300</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1325</v>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
+          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0am325025hfe_1.png, 0am325025hfe_2.png</t>
+          <t>0am325025l.png</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -5318,47 +5338,43 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>2879</v>
+        <v>8879</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1950</v>
+        <v>8443.5</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
-        </is>
-      </c>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0am325025j_1.png</t>
+          <t>0am325025m.png</t>
         </is>
       </c>
     </row>
     <row r="40" ht="78" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -5377,43 +5393,43 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1490</v>
+        <v>8979</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2300</v>
+        <v>12000</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1325</v>
+        <v>8378.5</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0am325025l.png</t>
+          <t>0am325025n_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="41" ht="78" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -5432,43 +5448,43 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>8879</v>
+        <v>979</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12000</v>
+        <v>1800</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>8443.5</v>
+        <v>980</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0am325025m.png</t>
+          <t>0am325025q_1.png</t>
         </is>
       </c>
     </row>
     <row r="42" ht="78" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -5487,43 +5503,43 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>8979</v>
+        <v>1479</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>8378.5</v>
+        <v>1475</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0am325025n_1.jpg</t>
+          <t>0am325025r_1.png</t>
         </is>
       </c>
     </row>
     <row r="43" ht="78" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -5542,43 +5558,43 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Ремкомплект Усиленный длинный шток 0AM325091E + DSG7 DQ200</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>979</v>
+        <v>4490</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1800</v>
+        <v>6000</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>980</v>
+        <v>3430</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0am325025q_1.png</t>
+          <t>0am325025u_1.png</t>
         </is>
       </c>
     </row>
     <row r="44" ht="78" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -5586,54 +5602,52 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1479</v>
+        <v>78475</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2500</v>
+        <v>90000</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>1475</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0am325025r_1.png</t>
+          <t>0am325025x_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="45" ht="78" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -5652,12 +5666,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный длинный шток 0AM325091E + DSG7 DQ200</t>
+          <t>Ремкомплект Усиленный короткий шток 0AM325091F + DSG7 DQ200</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -5667,161 +5681,53 @@
         <v>6000</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>3430</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0am325025u_1.png</t>
+          <t>0am325025z.png</t>
         </is>
       </c>
     </row>
     <row r="46" ht="78" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>0am325025x</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>0am325025ze</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>78475</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>90000</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2" t="n"/>
+          <t>Мехатроник DQ200 DSG7 0AM Новые соленоиды Bosch</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n">
+        <v>69302.22</v>
+      </c>
       <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0am325025x_1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="78" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>0am325025z</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект Усиленный короткий шток 0AM325091F + DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>4490</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>3430</v>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0am325025z.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="78" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>0am325025ze</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Мехатроник DQ200 DSG7 0AM Новые соленоиды Bosch</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n">
-        <v>69302.22</v>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Абсолютно новый мехатроник DSG7 DQ200 (0AM / 0CW) — гидравлическая часть
 В продаже полностью восстановленный до состояния нового мехатроник DSG7 DQ200 для коробок передач 0AM и 0CW. Узел собран с использованием новых оригинальных и OEM-компонентов, прошёл обязательную проверку и готов к установке.
@@ -5862,18 +5768,128 @@
 Капитальном ремонте коробки DQ200</t>
         </is>
       </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>(нет фото ни локально, ни на карточке)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="78" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>0am325025С</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0am325025С_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="78" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>0am325066AC</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1479</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>0am325066AC_1.png</t>
         </is>
       </c>
     </row>
     <row r="49" ht="78" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -5888,16 +5904,16 @@
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
@@ -5907,28 +5923,28 @@
         <v>2000</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>980</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0am325025С_1.png</t>
+          <t>0am325066ad_1.jpg, 0am325066ad_1.png</t>
         </is>
       </c>
     </row>
     <row r="50" ht="78" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -5943,47 +5959,47 @@
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>1479</v>
+        <v>8879</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1325</v>
+        <v>7347.3</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0am325066AC_1.png</t>
+          <t>0am325066ae_1.png, 0am325066ae_4.png</t>
         </is>
       </c>
     </row>
     <row r="51" ht="78" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -5998,47 +6014,51 @@
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>979</v>
+        <v>2879</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>980</v>
+        <v>2850</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad_1.jpg, 0am325066ad_1.png</t>
+          <t>0am325091e.png</t>
         </is>
       </c>
     </row>
     <row r="52" ht="78" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -6046,54 +6066,50 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 DSG7 DQ200</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>8879</v>
+        <v>8850</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>7347.3</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae_1.png, 0am325066ae_4.png</t>
+          <t>0am325091e-set_1.png</t>
         </is>
       </c>
     </row>
     <row r="53" ht="78" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -6112,12 +6128,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм 0AM325091F</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -6127,32 +6143,28 @@
         <v>5000</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2850</v>
+        <v>2950</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dsg7</t>
-        </is>
-      </c>
+          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0am325091e.png</t>
+          <t>0am325091f.png</t>
         </is>
       </c>
     </row>
     <row r="54" ht="78" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6167,12 +6179,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 DSG7 DQ200</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 DSG7 DQ200</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -6185,25 +6197,21 @@
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dsg7</t>
-        </is>
-      </c>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0am325091e-set_1.png</t>
+          <t>0am325091f-set_1.png</t>
         </is>
       </c>
     </row>
     <row r="55" ht="78" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6222,43 +6230,43 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм 0AM325091F</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>2879</v>
+        <v>2479</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2950</v>
+        <v>2447.15</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0am325091f.png</t>
+          <t>0am325477ae_1.png</t>
         </is>
       </c>
     </row>
     <row r="56" ht="78" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6269,43 +6277,45 @@
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200 10 шт оригинал</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>8850</v>
+        <v>11979</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J56" s="2" t="n"/>
+        <v>15000</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0am325091f-set_1.png</t>
+          <t>0ambset_1.png, 0ambset_2.png</t>
         </is>
       </c>
     </row>
     <row r="57" ht="78" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6313,54 +6323,52 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>2479</v>
+        <v>931</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>2447.15</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdsg7dq200</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae_1.png</t>
+          <t>0cw0am_1.png, 0cw0am_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="58" ht="78" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6371,45 +6379,49 @@
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200 10 шт оригинал</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>11979</v>
+        <v>16890</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкиdq200</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0ambset_1.png, 0ambset_2.png</t>
+          <t>0cw0am325025.png, 0cw0am325025_1.png, 0cw0am325025-2.png</t>
         </is>
       </c>
     </row>
     <row r="59" ht="78" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -6420,23 +6432,23 @@
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>931</v>
+        <v>850</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>49</v>
@@ -6444,25 +6456,25 @@
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
+          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкаdsg7dq200</t>
+          <t>#Прокладкаdq200dsg</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0cw0am_1.png, 0cw0am_1.jpg</t>
+          <t>0cw0amdsgdq200_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="60" ht="78" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6473,49 +6485,49 @@
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+          <t>Прокладка электронной платы DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>16890</v>
+        <v>1290</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>25000</v>
+        <v>2000</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкиdq200</t>
+          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025.png, 0cw0am325025_1.png, 0cw0am325025-2.png</t>
+          <t>0cw325025h_1.png</t>
         </is>
       </c>
     </row>
     <row r="61" ht="78" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -6526,49 +6538,45 @@
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>850</v>
+        <v>1490</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdq200dsg</t>
-        </is>
-      </c>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200_1.jpg</t>
+          <t>0сц_1.png, 0сц_2.png, 0сц_3.png, 0сц_4.png, 0сц_5.png, 0сц_6.png, 0сц_7.png</t>
         </is>
       </c>
     </row>
     <row r="62" ht="78" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -6576,52 +6584,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы DSG7 DQ200 0AM927769N</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1290</v>
+        <v>979</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="K62" s="2" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>980</v>
+      </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
-        </is>
-      </c>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0cw325025h_1.png</t>
+          <t>122390AK-AF_1.png, 122390AK-AF_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="63" ht="78" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -6629,19 +6639,23 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
@@ -6651,26 +6665,28 @@
         <v>2500</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="K63" s="2" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>1319.7</v>
+      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0сц_1.png, 0сц_2.png, 0сц_3.png, 0сц_4.png, 0сц_5.png, 0сц_6.png, 0сц_7.png</t>
+          <t>122390AKAF_1.png</t>
         </is>
       </c>
     </row>
     <row r="64" ht="78" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -6689,43 +6705,43 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>979</v>
+        <v>1479</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>980</v>
+        <v>1225</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>122390AK-AF_1.png, 122390AK-AF_1.jpg</t>
+          <t>123014‑AF_1.png, 123014‑AF_2.png</t>
         </is>
       </c>
     </row>
     <row r="65" ht="78" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -6744,50 +6760,50 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1490</v>
+        <v>58900</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1319.7</v>
+        <v>40052</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf011e</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>122390AKAF_1.png</t>
+          <t>31705-1XF0C_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="66" ht="78" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>31705-1XF1A</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -6795,131 +6811,21 @@
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>1479</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>28</v>
-      </c>
+          <t>Гидроблок JF011E Старое поколение Nissan Mitsubishi Renault</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n">
-        <v>1225</v>
+        <v>40052</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>123014‑AF_1.png, 123014‑AF_2.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="78" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>58900</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>80000</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>40052</v>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>#гидроблокjf011e</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>31705-1XF0C_1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="78" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок JF011E Старое поколение Nissan Mitsubishi Renault</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="n">
-        <v>40052</v>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E Старое поколение для вариатора CVT RE0F10A. Восстанавливает давление масла и стабильную работу трансмиссии. Прямая замена штатного узла без доработок.
 Гидроблок вариатора JF011E Старое поколение — управляющий узел CVT-коробки, отвечающий за распределение давления масла и работу соленоидов. Применяется в вариаторах RE0F10A и устанавливается на автомобили Nissan, Mitsubishi, Renault и Jeep.
@@ -6947,18 +6853,132 @@
 гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi ремонт вариатора jf011e</t>
         </is>
       </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>(нет фото ни локально, ни на карточке)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="78" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>31705-X428B</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>58900</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>42408</v>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>31705-X428B_1.png, 31705-X428B_2.png, 31705-X428B_3.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="78" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>317053TX0C</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>58900</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>40052</v>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
+        </is>
+      </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>317053TX0C_1.png</t>
         </is>
       </c>
     </row>
     <row r="69" ht="78" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -6973,51 +6993,47 @@
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>58900</v>
+        <v>999</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>80000</v>
+        <v>2000</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>42408</v>
+        <v>980</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
-        </is>
-      </c>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>31705-X428B_1.png, 31705-X428B_2.png, 31705-X428B_3.png</t>
+          <t>55565480_1.png</t>
         </is>
       </c>
     </row>
     <row r="70" ht="78" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -7025,54 +7041,46 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>58900</v>
+        <v>19800</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>80000</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>40052</v>
-      </c>
+        <v>25000</v>
+      </c>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>317053TX0C_1.png</t>
+          <t>6t30_1.png</t>
         </is>
       </c>
     </row>
     <row r="71" ht="78" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -7087,47 +7095,47 @@
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>999</v>
+        <v>3850</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>980</v>
+        <v>1515.9</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>55565480_1.png</t>
+          <t>DQ500-a-1.png, DQ500_a-2.png, DQ500_1.png, DQ500_3.png</t>
         </is>
       </c>
     </row>
     <row r="72" ht="78" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -7142,125 +7150,143 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>19800</v>
+        <v>979</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J72" s="2" t="n"/>
+        <v>1500</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>44</v>
+      </c>
       <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>6t30_1.png</t>
+          <t>Dq200dsg7_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="73" ht="78" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>DF-DQ250-ALU-KIT</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr"/>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045+масляный фильтр DSG6</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
-      <c r="J73" s="2" t="n"/>
-      <c r="K73" s="2" t="n">
-        <v>2150</v>
-      </c>
+          <t>пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>8890</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
-Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>Dq200dsg70am0cw_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="74" ht="78" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DF-DQ500-FH-KIT</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+          <t>Dq500</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + масляный фильтр DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="n"/>
-      <c r="J74" s="2" t="n"/>
-      <c r="K74" s="2" t="n">
-        <v>1564.8</v>
-      </c>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>3879</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Комплект корпуса масляного фильтра с фильтром для роботизированной коробки передач DSG7 DQ500 (0BH).
-Подходит для автомобилей VAG с 7-ступенчатой мокрой DSG DQ500.
-Обеспечивает качественную фильтрацию масла, корпус фильтра dq500 улучшает теплоотвод и уменьшает температуру масла
-Рекомендуется при обслуживании и ремонте DSG 7 DQ500.</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>(нет фото ни локально, ни на карточке)</t>
+          <t>Dq500_1.jpg, Dq500_2.png</t>
         </is>
       </c>
     </row>
     <row r="75" ht="78" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -7271,45 +7297,49 @@
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>3850</v>
+        <v>4741</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>#корпусмасляногофильтраEA888</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>DQ500-a-1.png, DQ500_a-2.png, DQ500_1.png, DQ500_3.png</t>
+          <t>EA888_1.png</t>
         </is>
       </c>
     </row>
     <row r="76" ht="78" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -7324,45 +7354,41 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>979</v>
+        <v>6690</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdq200</t>
-        </is>
-      </c>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7_1.jpg</t>
+          <t>EA888gen3_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="77" ht="78" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -7373,45 +7399,45 @@
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="n"/>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>8890</v>
+        <v>2366</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12000</v>
+        <v>3500</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw_1.jpg</t>
+          <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
         </is>
       </c>
     </row>
     <row r="78" ht="78" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -7422,98 +7448,86 @@
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>3879</v>
+        <v>100</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Dq500_1.jpg, Dq500_2.png</t>
+          <t>TEST001_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="79" ht="78" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>EA888</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
+          <t>TESTWB001</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Корпус масляного фильтра двигателя EA888</t>
-        </is>
-      </c>
+      <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра двигателя EA888</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>4741</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K79" s="2" t="n"/>
+          <t>Тестовый товар — не публикуется</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>#корпусмасляногофильтраEA888</t>
-        </is>
-      </c>
+          <t>Тестовая карточка для проверки автоматизации</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>EA888_1.png</t>
+          <t>TESTWB001_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="80" ht="78" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -7521,48 +7535,54 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>6690</v>
+        <v>979</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K80" s="2" t="n"/>
+        <v>93</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>690</v>
+      </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3_1.jpg</t>
+          <t>WHT001922_1.png</t>
         </is>
       </c>
     </row>
     <row r="81" ht="78" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -7573,45 +7593,43 @@
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>2366</v>
+        <v>1490</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>16</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="J81" s="2" t="n"/>
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3_1.png, Ea888gen3_2.png</t>
+          <t>filtr-setka-0b5-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="82" ht="78" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -7626,44 +7644,46 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Новый оригинальный гидроаккумулятор VAG DSG7 DQ200</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>100</v>
+        <v>8890</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J82" s="2" t="n"/>
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>TEST001_2.jpg</t>
+          <t>gidroakkumulyator-orig_3.png</t>
         </is>
       </c>
     </row>
     <row r="83" ht="78" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr"/>
+          <t>jf011e</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Действующий</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Действующий</t>
@@ -7673,35 +7693,45 @@
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар — не публикуется</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="n"/>
-      <c r="J83" s="2" t="n"/>
+          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>12979</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K83" s="2" t="n">
-        <v>100</v>
+        <v>15000</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации</t>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>TESTWB001_2.jpg</t>
+          <t>jf011e_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="84" ht="78" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -7709,54 +7739,46 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="I84" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="J84" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>690</v>
-      </c>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>WHT001922_1.png</t>
+          <t>klipsy-shtokov-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="85" ht="78" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -7767,43 +7789,43 @@
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>1490</v>
+        <v>3879</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2500</v>
+        <v>6000</v>
       </c>
       <c r="J85" s="2" t="n"/>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig_1.png</t>
+          <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
         </is>
       </c>
     </row>
     <row r="86" ht="78" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -7814,43 +7836,45 @@
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Новый оригинальный гидроаккумулятор VAG DSG7 DQ200</t>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>8890</v>
+        <v>990</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J86" s="2" t="n"/>
+        <v>1500</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
+          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig_3.png</t>
+          <t>nakladki-pedali_1.png, nakladki-pedali_2.png</t>
         </is>
       </c>
     </row>
     <row r="87" ht="78" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -7858,54 +7882,46 @@
           <t>Действующий</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
+      <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>12979</v>
+        <v>2890</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>15000</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>jf011e_1.jpg</t>
+          <t>planka-solenoid-2sht_1.png</t>
         </is>
       </c>
     </row>
     <row r="88" ht="78" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -7920,39 +7936,43 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200 без</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="J88" s="2" t="n"/>
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht_1.png</t>
+          <t>plastiny-solenoid-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="89" ht="78" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -7963,43 +7983,43 @@
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159</t>
+          <t>фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>3879</v>
+        <v>7500</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="J89" s="2" t="n"/>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159_1.png, korpus-filtra-0bh325159_2.png</t>
+          <t>plita-filtr_1.png</t>
         </is>
       </c>
     </row>
     <row r="90" ht="78" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -8010,45 +8030,43 @@
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>990</v>
+        <v>8500</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="J90" s="2" t="n"/>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>nakladki-pedali_1.png, nakladki-pedali_2.png</t>
+          <t>plita-filtr-pylniki_1.png</t>
         </is>
       </c>
     </row>
     <row r="91" ht="78" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -8063,39 +8081,39 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>2890</v>
+        <v>8500</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>4000</v>
+        <v>13000</v>
       </c>
       <c r="J91" s="2" t="n"/>
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht_1.png</t>
+          <t>plita-filtr-pylniki-orig_1.png</t>
         </is>
       </c>
     </row>
     <row r="92" ht="78" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -8110,43 +8128,39 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200 без</t>
+          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>990</v>
+        <v>9500</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="J92" s="2" t="n"/>
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
-        </is>
-      </c>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig_1.png</t>
+          <t>plita-filtr-pylniki-sal_1.png</t>
         </is>
       </c>
     </row>
     <row r="93" ht="78" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -8157,20 +8171,20 @@
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="n"/>
       <c r="E93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>